--- a/inst/extdata/MetricScoring.xlsx
+++ b/inst/extdata/MetricScoring.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BioMonTools\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D62549D-AAB7-43C8-9C8C-A05F273E4FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E6F5AA-8209-4110-A159-54C71F9FEC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="1" r:id="rId1"/>
@@ -23,8 +23,8 @@
     <sheet name="ToDo_index" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">index.scoring!$A$1:$Z$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">metric.scoring!$A$1:$AP$802</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">index.scoring!$A$1:$Z$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">metric.scoring!$A$1:$AP$803</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ScoringRegimes!$A$5:$C$17</definedName>
     <definedName name="FileName">NOTES!$B$8</definedName>
   </definedNames>
@@ -1644,6 +1644,294 @@
         </r>
       </text>
     </comment>
+    <comment ref="K111" authorId="0" shapeId="0" xr:uid="{95AD45BA-D71F-4A27-92ED-EF9216D767C8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Leppo, Erik:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Report is 2.6 and 2.7 as cutoffs.  For divide.  Use 2.65 so if rouding should be ok.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K112" authorId="0" shapeId="0" xr:uid="{70C9F623-0A0C-4C1F-A620-B502F0E68E36}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Leppo, Erik:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Report is 2.6 and 2.7 as cutoffs.  For divide.  Use 2.65 so if rouding should be ok.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K113" authorId="0" shapeId="0" xr:uid="{7E1C6060-B64A-4EC4-A2B0-D6C9738C0A85}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Leppo, Erik:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Report is 2.6 and 2.7 as cutoffs.  For divide.  Use 2.65 so if rouding should be ok.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K114" authorId="0" shapeId="0" xr:uid="{3B1DD8B9-AD68-4930-9BF3-88BA6D460296}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Leppo, Erik:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Report is 2.6 and 2.7 as cutoffs.  For divide.  Use 2.65 so if rouding should be ok.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K115" authorId="0" shapeId="0" xr:uid="{541693CE-2BA1-431A-A4E0-052062F929D7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Leppo, Erik:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Report is 2.6 and 2.7 as cutoffs.  For divide.  Use 2.65 so if rouding should be ok.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K116" authorId="0" shapeId="0" xr:uid="{56BFE27A-1311-46ED-81B3-CE7FA43CCDB5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Leppo, Erik:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Report is 2.6 and 2.7 as cutoffs.  For divide.  Use 2.65 so if rouding should be ok.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K117" authorId="0" shapeId="0" xr:uid="{F953B359-6421-4FB3-B5CB-337BACC1AD44}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Leppo, Erik:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Report is 2.6 and 2.7 as cutoffs.  For divide.  Use 2.65 so if rouding should be ok.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K118" authorId="0" shapeId="0" xr:uid="{D5E8C9B5-16AA-436E-A6E3-1413ADF84065}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Leppo, Erik:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Report is 2.6 and 2.7 as cutoffs.  For divide.  Use 2.65 so if rouding should be ok.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K119" authorId="0" shapeId="0" xr:uid="{09A1E68C-6ED8-4820-9949-F2EB8E605EAD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Leppo, Erik:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Report is 2.6 and 2.7 as cutoffs.  For divide.  Use 2.65 so if rouding should be ok.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K120" authorId="0" shapeId="0" xr:uid="{0D80A14D-063C-4E28-A3A6-746806DF5550}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Leppo, Erik:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Report is 2.6 and 2.7 as cutoffs.  For divide.  Use 2.65 so if rouding should be ok.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K121" authorId="0" shapeId="0" xr:uid="{4FF0FCE1-6A7E-436F-887E-888BA5328EFA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Leppo, Erik:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Report is 2.6 and 2.7 as cutoffs.  For divide.  Use 2.65 so if rouding should be ok.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K122" authorId="0" shapeId="0" xr:uid="{CFF85006-E8A3-4BDC-AF4D-97573717BF42}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Leppo, Erik:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Report is 2.6 and 2.7 as cutoffs.  For divide.  Use 2.65 so if rouding should be ok.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -1671,7 +1959,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9958" uniqueCount="1044">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10092" uniqueCount="1061">
   <si>
     <t>Erik.Leppo@tetratech.com</t>
   </si>
@@ -4803,6 +5091,57 @@
   </si>
   <si>
     <t>17.81</t>
+  </si>
+  <si>
+    <t>ChesBay_2002</t>
+  </si>
+  <si>
+    <t>Chesapeake Bay BIBI (benthos), based on Alden et al. 2002, an update of Weisberg et al. 1997</t>
+  </si>
+  <si>
+    <t>https://sci.odu.edu/chesapeakebay/data/benthic/BIBIcalc.pdf</t>
+  </si>
+  <si>
+    <t>TF</t>
+  </si>
+  <si>
+    <t>OL</t>
+  </si>
+  <si>
+    <t>Meets restoration goals</t>
+  </si>
+  <si>
+    <t>Marginal</t>
+  </si>
+  <si>
+    <t>LM_abund</t>
+  </si>
+  <si>
+    <t>HM_sand_abund</t>
+  </si>
+  <si>
+    <t>HM_mud_abund</t>
+  </si>
+  <si>
+    <t>PO_sand_abund</t>
+  </si>
+  <si>
+    <t>PO_mud_abund</t>
+  </si>
+  <si>
+    <t>LM_biomass</t>
+  </si>
+  <si>
+    <t>HM_sand_biomass</t>
+  </si>
+  <si>
+    <t>HM_mud_biomass</t>
+  </si>
+  <si>
+    <t>PO_sand_biomass</t>
+  </si>
+  <si>
+    <t>PO_mud_biomass</t>
   </si>
 </sst>
 </file>
@@ -5081,7 +5420,7 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3"/>
@@ -5127,7 +5466,6 @@
     <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Bad" xfId="6" builtinId="27"/>
@@ -5144,16 +5482,6 @@
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5309,6 +5637,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color auto="1"/>
       </font>
       <fill>
@@ -5389,11 +5727,81 @@
     </dxf>
     <dxf>
       <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5459,6 +5867,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color auto="1"/>
       </font>
       <fill>
@@ -5474,6 +5902,106 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5539,11 +6067,61 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color auto="1"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5589,6 +6167,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -5604,6 +6192,166 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5649,171 +6397,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color auto="1"/>
+        <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5899,26 +6497,6 @@
     </dxf>
     <dxf>
       <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -5949,11 +6527,81 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5979,11 +6627,31 @@
     </dxf>
     <dxf>
       <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5999,11 +6667,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6019,16 +6687,6 @@
     </dxf>
     <dxf>
       <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -6039,331 +6697,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color auto="1"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7549,10 +7887,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A70181-B22C-4671-9C22-4B8DA5FE66AB}">
-  <sheetPr codeName="Sheet1">
+  <sheetPr codeName="Sheet1" filterMode="1">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:AP802"/>
+  <dimension ref="A1:AP803"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" customWidth="1"/>
@@ -8396,7 +8734,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>525</v>
       </c>
@@ -8428,7 +8766,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>525</v>
       </c>
@@ -8460,7 +8798,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>525</v>
       </c>
@@ -8492,7 +8830,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>525</v>
       </c>
@@ -8524,7 +8862,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>525</v>
       </c>
@@ -8556,7 +8894,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>525</v>
       </c>
@@ -8588,7 +8926,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>525</v>
       </c>
@@ -8620,7 +8958,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>525</v>
       </c>
@@ -8652,7 +8990,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>525</v>
       </c>
@@ -8684,7 +9022,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>525</v>
       </c>
@@ -8716,7 +9054,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>525</v>
       </c>
@@ -8748,7 +9086,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>525</v>
       </c>
@@ -8780,7 +9118,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>525</v>
       </c>
@@ -8812,7 +9150,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>525</v>
       </c>
@@ -8844,7 +9182,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>525</v>
       </c>
@@ -8876,7 +9214,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>525</v>
       </c>
@@ -8908,7 +9246,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>525</v>
       </c>
@@ -8940,7 +9278,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>525</v>
       </c>
@@ -8972,7 +9310,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>525</v>
       </c>
@@ -9004,7 +9342,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>525</v>
       </c>
@@ -9036,7 +9374,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>525</v>
       </c>
@@ -9068,7 +9406,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>525</v>
       </c>
@@ -13597,7 +13935,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>300</v>
       </c>
@@ -13662,7 +14000,7 @@
         <v>11.86</v>
       </c>
     </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>300</v>
       </c>
@@ -13730,7 +14068,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="193" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>300</v>
       </c>
@@ -13795,7 +14133,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="194" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>300</v>
       </c>
@@ -13860,7 +14198,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="195" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>300</v>
       </c>
@@ -13925,7 +14263,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="196" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>300</v>
       </c>
@@ -13990,7 +14328,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="197" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>300</v>
       </c>
@@ -14049,7 +14387,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="198" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>300</v>
       </c>
@@ -14126,7 +14464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>300</v>
       </c>
@@ -14191,7 +14529,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="200" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>300</v>
       </c>
@@ -14256,7 +14594,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="201" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>300</v>
       </c>
@@ -14321,7 +14659,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="202" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>300</v>
       </c>
@@ -14386,7 +14724,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="203" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>300</v>
       </c>
@@ -14451,7 +14789,7 @@
         <v>11.86</v>
       </c>
     </row>
-    <row r="204" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>300</v>
       </c>
@@ -14519,7 +14857,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="205" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>300</v>
       </c>
@@ -14587,7 +14925,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="206" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>300</v>
       </c>
@@ -14652,7 +14990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="207" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>300</v>
       </c>
@@ -14717,7 +15055,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="208" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>300</v>
       </c>
@@ -14785,7 +15123,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="209" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>300</v>
       </c>
@@ -14850,7 +15188,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="210" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>300</v>
       </c>
@@ -14927,7 +15265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>300</v>
       </c>
@@ -14992,7 +15330,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="212" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>300</v>
       </c>
@@ -15057,7 +15395,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="213" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>300</v>
       </c>
@@ -15122,7 +15460,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="214" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>300</v>
       </c>
@@ -15187,7 +15525,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="215" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>300</v>
       </c>
@@ -15252,7 +15590,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="216" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>300</v>
       </c>
@@ -15320,7 +15658,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="217" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>300</v>
       </c>
@@ -15385,7 +15723,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="218" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>300</v>
       </c>
@@ -15452,7 +15790,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="219" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>300</v>
       </c>
@@ -15520,7 +15858,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="220" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>300</v>
       </c>
@@ -15585,7 +15923,7 @@
         <v>3.06</v>
       </c>
     </row>
-    <row r="221" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>300</v>
       </c>
@@ -15650,7 +15988,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="222" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>300</v>
       </c>
@@ -15727,7 +16065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>300</v>
       </c>
@@ -15792,7 +16130,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="224" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>300</v>
       </c>
@@ -15857,7 +16195,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="225" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>300</v>
       </c>
@@ -15922,7 +16260,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="226" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>300</v>
       </c>
@@ -15987,7 +16325,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="227" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>300</v>
       </c>
@@ -16052,7 +16390,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="228" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>300</v>
       </c>
@@ -16120,7 +16458,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="229" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>300</v>
       </c>
@@ -16188,7 +16526,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="230" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>300</v>
       </c>
@@ -16255,7 +16593,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="231" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>300</v>
       </c>
@@ -16323,7 +16661,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="232" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>300</v>
       </c>
@@ -16388,7 +16726,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="233" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>300</v>
       </c>
@@ -16453,7 +16791,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="234" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>300</v>
       </c>
@@ -16530,7 +16868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>300</v>
       </c>
@@ -16595,7 +16933,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="236" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>300</v>
       </c>
@@ -16660,7 +16998,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="237" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>300</v>
       </c>
@@ -16725,7 +17063,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="238" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>300</v>
       </c>
@@ -16790,7 +17128,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="239" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>300</v>
       </c>
@@ -16855,7 +17193,7 @@
         <v>9.66</v>
       </c>
     </row>
-    <row r="240" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>300</v>
       </c>
@@ -16920,7 +17258,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="241" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>300</v>
       </c>
@@ -16985,7 +17323,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="242" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>300</v>
       </c>
@@ -17050,7 +17388,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="243" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>300</v>
       </c>
@@ -17115,7 +17453,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="244" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>300</v>
       </c>
@@ -17180,7 +17518,7 @@
         <v>1.79</v>
       </c>
     </row>
-    <row r="245" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>300</v>
       </c>
@@ -17245,7 +17583,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="246" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>300</v>
       </c>
@@ -17322,7 +17660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>300</v>
       </c>
@@ -17387,7 +17725,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="248" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>300</v>
       </c>
@@ -17452,7 +17790,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="249" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>300</v>
       </c>
@@ -17517,7 +17855,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="250" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>300</v>
       </c>
@@ -17582,7 +17920,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="251" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>300</v>
       </c>
@@ -17647,7 +17985,7 @@
         <v>9.66</v>
       </c>
     </row>
-    <row r="252" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>300</v>
       </c>
@@ -17712,7 +18050,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="253" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>300</v>
       </c>
@@ -17777,7 +18115,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="254" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>300</v>
       </c>
@@ -17842,7 +18180,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="255" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>300</v>
       </c>
@@ -17907,7 +18245,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="256" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>300</v>
       </c>
@@ -17972,7 +18310,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="257" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>300</v>
       </c>
@@ -18037,7 +18375,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="258" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>300</v>
       </c>
@@ -18114,7 +18452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>300</v>
       </c>
@@ -18179,7 +18517,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="260" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>300</v>
       </c>
@@ -18244,7 +18582,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="261" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>300</v>
       </c>
@@ -18309,7 +18647,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="262" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>300</v>
       </c>
@@ -18374,7 +18712,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="263" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>300</v>
       </c>
@@ -18451,7 +18789,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="264" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>300</v>
       </c>
@@ -18528,7 +18866,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="265" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>300</v>
       </c>
@@ -18605,7 +18943,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="266" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>300</v>
       </c>
@@ -18682,7 +19020,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="267" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>300</v>
       </c>
@@ -18759,7 +19097,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="268" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>300</v>
       </c>
@@ -18836,7 +19174,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="269" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>300</v>
       </c>
@@ -18913,7 +19251,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="270" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>300</v>
       </c>
@@ -18990,7 +19328,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="271" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>300</v>
       </c>
@@ -19067,7 +19405,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="272" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>300</v>
       </c>
@@ -19144,7 +19482,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="273" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>300</v>
       </c>
@@ -19221,7 +19559,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="274" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>300</v>
       </c>
@@ -22751,7 +23089,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="390" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>479</v>
       </c>
@@ -22816,7 +23154,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="391" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>479</v>
       </c>
@@ -22881,7 +23219,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="392" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>479</v>
       </c>
@@ -22946,7 +23284,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="393" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>479</v>
       </c>
@@ -23011,7 +23349,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="394" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>479</v>
       </c>
@@ -23076,7 +23414,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="395" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>479</v>
       </c>
@@ -23141,7 +23479,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="396" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>479</v>
       </c>
@@ -23200,7 +23538,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="397" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>479</v>
       </c>
@@ -23277,7 +23615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>479</v>
       </c>
@@ -23342,7 +23680,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="399" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>479</v>
       </c>
@@ -23407,7 +23745,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="400" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>479</v>
       </c>
@@ -23472,7 +23810,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="401" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>479</v>
       </c>
@@ -23537,7 +23875,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="402" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>479</v>
       </c>
@@ -23602,7 +23940,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="403" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>479</v>
       </c>
@@ -23667,7 +24005,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="404" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>479</v>
       </c>
@@ -23732,7 +24070,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="405" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>479</v>
       </c>
@@ -23797,7 +24135,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="406" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>479</v>
       </c>
@@ -23862,7 +24200,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="407" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>479</v>
       </c>
@@ -23927,7 +24265,7 @@
         <v>-0.19</v>
       </c>
     </row>
-    <row r="408" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>479</v>
       </c>
@@ -23992,7 +24330,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="409" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>479</v>
       </c>
@@ -24069,7 +24407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>479</v>
       </c>
@@ -24134,7 +24472,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="411" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>479</v>
       </c>
@@ -24199,7 +24537,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="412" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>479</v>
       </c>
@@ -24264,7 +24602,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="413" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>479</v>
       </c>
@@ -24329,7 +24667,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="414" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>479</v>
       </c>
@@ -24394,7 +24732,7 @@
         <v>8.49</v>
       </c>
     </row>
-    <row r="415" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>479</v>
       </c>
@@ -24459,7 +24797,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="416" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>479</v>
       </c>
@@ -24524,7 +24862,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="417" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>479</v>
       </c>
@@ -24589,7 +24927,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="418" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>479</v>
       </c>
@@ -24654,7 +24992,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="419" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>479</v>
       </c>
@@ -24719,7 +25057,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="420" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>479</v>
       </c>
@@ -24784,7 +25122,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="421" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>479</v>
       </c>
@@ -24861,7 +25199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>479</v>
       </c>
@@ -24926,7 +25264,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="423" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>479</v>
       </c>
@@ -24991,7 +25329,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="424" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>479</v>
       </c>
@@ -25056,7 +25394,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="425" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>479</v>
       </c>
@@ -25121,7 +25459,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="426" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>479</v>
       </c>
@@ -25186,7 +25524,7 @@
         <v>8.49</v>
       </c>
     </row>
-    <row r="427" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>479</v>
       </c>
@@ -25251,7 +25589,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="428" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>479</v>
       </c>
@@ -25316,7 +25654,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="429" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>479</v>
       </c>
@@ -25381,7 +25719,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="430" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>479</v>
       </c>
@@ -25446,7 +25784,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="431" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>479</v>
       </c>
@@ -25511,7 +25849,7 @@
         <v>-0.37</v>
       </c>
     </row>
-    <row r="432" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>479</v>
       </c>
@@ -25576,7 +25914,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="433" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>479</v>
       </c>
@@ -25653,7 +25991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>479</v>
       </c>
@@ -25718,7 +26056,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="435" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>479</v>
       </c>
@@ -25783,7 +26121,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="436" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>479</v>
       </c>
@@ -25848,7 +26186,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="437" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>479</v>
       </c>
@@ -25913,7 +26251,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="438" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>479</v>
       </c>
@@ -25978,7 +26316,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="439" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>479</v>
       </c>
@@ -26043,7 +26381,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="440" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>479</v>
       </c>
@@ -26108,7 +26446,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="441" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>479</v>
       </c>
@@ -26173,7 +26511,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="442" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>479</v>
       </c>
@@ -26238,7 +26576,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="443" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>479</v>
       </c>
@@ -26303,7 +26641,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="444" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>479</v>
       </c>
@@ -26368,7 +26706,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="445" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>479</v>
       </c>
@@ -26445,7 +26783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>479</v>
       </c>
@@ -26510,7 +26848,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="447" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>479</v>
       </c>
@@ -26575,7 +26913,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="448" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>479</v>
       </c>
@@ -26640,7 +26978,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="449" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>479</v>
       </c>
@@ -26705,7 +27043,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="450" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>479</v>
       </c>
@@ -26770,7 +27108,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="451" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>479</v>
       </c>
@@ -26835,7 +27173,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="452" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>479</v>
       </c>
@@ -26900,7 +27238,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="453" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>479</v>
       </c>
@@ -26965,7 +27303,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="454" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>479</v>
       </c>
@@ -27030,7 +27368,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="455" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>479</v>
       </c>
@@ -27095,7 +27433,7 @@
         <v>-0.51</v>
       </c>
     </row>
-    <row r="456" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>479</v>
       </c>
@@ -27160,7 +27498,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="457" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>479</v>
       </c>
@@ -27237,7 +27575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="458" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>479</v>
       </c>
@@ -27302,7 +27640,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="459" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>479</v>
       </c>
@@ -27367,7 +27705,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="460" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>479</v>
       </c>
@@ -27432,7 +27770,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="461" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>479</v>
       </c>
@@ -27497,7 +27835,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="462" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>479</v>
       </c>
@@ -27574,7 +27912,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="463" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>479</v>
       </c>
@@ -27651,7 +27989,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="464" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>479</v>
       </c>
@@ -27728,7 +28066,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="465" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>479</v>
       </c>
@@ -27805,7 +28143,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="466" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>479</v>
       </c>
@@ -27882,7 +28220,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="467" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>479</v>
       </c>
@@ -27959,7 +28297,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="468" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>479</v>
       </c>
@@ -28036,7 +28374,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="469" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>479</v>
       </c>
@@ -28113,7 +28451,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="470" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>479</v>
       </c>
@@ -28190,7 +28528,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="471" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>479</v>
       </c>
@@ -28267,7 +28605,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="472" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>479</v>
       </c>
@@ -28344,7 +28682,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="473" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>479</v>
       </c>
@@ -31116,7 +31454,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="550" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>584</v>
       </c>
@@ -31154,7 +31492,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="551" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>584</v>
       </c>
@@ -31195,7 +31533,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="552" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>584</v>
       </c>
@@ -31236,7 +31574,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="553" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>584</v>
       </c>
@@ -31274,7 +31612,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="554" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>584</v>
       </c>
@@ -31306,7 +31644,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="555" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>584</v>
       </c>
@@ -31338,7 +31676,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="556" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>584</v>
       </c>
@@ -31370,7 +31708,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="557" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>584</v>
       </c>
@@ -31402,7 +31740,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="558" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>584</v>
       </c>
@@ -31437,7 +31775,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="559" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>584</v>
       </c>
@@ -31472,7 +31810,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="560" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>584</v>
       </c>
@@ -31507,7 +31845,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="561" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>602</v>
       </c>
@@ -31542,7 +31880,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="562" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>602</v>
       </c>
@@ -31577,7 +31915,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="563" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>602</v>
       </c>
@@ -31612,7 +31950,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="564" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>602</v>
       </c>
@@ -31647,7 +31985,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="565" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>602</v>
       </c>
@@ -31682,7 +32020,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="566" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>602</v>
       </c>
@@ -31717,7 +32055,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="567" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>602</v>
       </c>
@@ -31752,7 +32090,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="568" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>602</v>
       </c>
@@ -31787,7 +32125,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="569" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>602</v>
       </c>
@@ -31822,7 +32160,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="570" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>602</v>
       </c>
@@ -35522,7 +35860,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="677" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>726</v>
       </c>
@@ -35569,7 +35907,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="678" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>726</v>
       </c>
@@ -35616,7 +35954,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="679" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>726</v>
       </c>
@@ -35657,7 +35995,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="680" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>726</v>
       </c>
@@ -35698,7 +36036,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="681" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>726</v>
       </c>
@@ -35742,7 +36080,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="682" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>726</v>
       </c>
@@ -35783,7 +36121,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="683" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>726</v>
       </c>
@@ -35824,7 +36162,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="684" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>726</v>
       </c>
@@ -35865,7 +36203,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="685" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>726</v>
       </c>
@@ -35906,7 +36244,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="686" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>726</v>
       </c>
@@ -35947,7 +36285,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="687" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>726</v>
       </c>
@@ -35988,7 +36326,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="688" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>726</v>
       </c>
@@ -36029,7 +36367,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="689" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>726</v>
       </c>
@@ -36070,7 +36408,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="690" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>726</v>
       </c>
@@ -36111,7 +36449,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="691" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>726</v>
       </c>
@@ -36152,7 +36490,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="692" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>726</v>
       </c>
@@ -36193,7 +36531,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="693" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>726</v>
       </c>
@@ -36234,7 +36572,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="694" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>726</v>
       </c>
@@ -36275,7 +36613,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="695" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>726</v>
       </c>
@@ -36316,7 +36654,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="696" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>726</v>
       </c>
@@ -36357,7 +36695,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="697" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>726</v>
       </c>
@@ -36398,7 +36736,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="698" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>726</v>
       </c>
@@ -36439,7 +36777,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="699" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>726</v>
       </c>
@@ -36480,7 +36818,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="700" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>726</v>
       </c>
@@ -36521,7 +36859,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="701" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>726</v>
       </c>
@@ -36556,7 +36894,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="702" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>726</v>
       </c>
@@ -36597,7 +36935,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="703" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>726</v>
       </c>
@@ -36638,7 +36976,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="704" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>726</v>
       </c>
@@ -36679,7 +37017,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="705" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>726</v>
       </c>
@@ -36720,7 +37058,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="706" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>726</v>
       </c>
@@ -36761,7 +37099,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="707" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>726</v>
       </c>
@@ -36802,7 +37140,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="708" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>726</v>
       </c>
@@ -36843,7 +37181,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="709" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>726</v>
       </c>
@@ -36884,7 +37222,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="710" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>726</v>
       </c>
@@ -36925,7 +37263,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="711" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>726</v>
       </c>
@@ -36960,7 +37298,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="712" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>726</v>
       </c>
@@ -37001,7 +37339,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="713" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>726</v>
       </c>
@@ -37042,7 +37380,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="714" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>726</v>
       </c>
@@ -37083,7 +37421,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="715" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>726</v>
       </c>
@@ -37124,7 +37462,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="716" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>726</v>
       </c>
@@ -37165,7 +37503,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="717" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>726</v>
       </c>
@@ -37197,7 +37535,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="718" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>726</v>
       </c>
@@ -37229,7 +37567,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="719" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>726</v>
       </c>
@@ -37267,7 +37605,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="720" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>726</v>
       </c>
@@ -37302,7 +37640,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="721" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>726</v>
       </c>
@@ -37337,7 +37675,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="722" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>726</v>
       </c>
@@ -37369,7 +37707,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="723" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>726</v>
       </c>
@@ -37401,7 +37739,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="724" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>726</v>
       </c>
@@ -37788,7 +38126,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="736" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>726</v>
       </c>
@@ -37829,7 +38167,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="737" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>726</v>
       </c>
@@ -37876,7 +38214,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="738" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>726</v>
       </c>
@@ -37917,7 +38255,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="739" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>726</v>
       </c>
@@ -37958,7 +38296,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="740" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>726</v>
       </c>
@@ -37999,7 +38337,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="741" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>726</v>
       </c>
@@ -38040,7 +38378,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="742" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>726</v>
       </c>
@@ -38081,7 +38419,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="743" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>726</v>
       </c>
@@ -38128,7 +38466,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="744" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>726</v>
       </c>
@@ -38169,7 +38507,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="745" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>726</v>
       </c>
@@ -38210,7 +38548,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="746" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>726</v>
       </c>
@@ -38251,7 +38589,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="747" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>726</v>
       </c>
@@ -38292,7 +38630,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="748" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>726</v>
       </c>
@@ -38333,7 +38671,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="749" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>726</v>
       </c>
@@ -38374,7 +38712,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="750" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>726</v>
       </c>
@@ -38415,7 +38753,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="751" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>726</v>
       </c>
@@ -38456,7 +38794,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="752" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>726</v>
       </c>
@@ -38497,7 +38835,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="753" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>726</v>
       </c>
@@ -38538,7 +38876,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="754" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>726</v>
       </c>
@@ -38579,7 +38917,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="755" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>726</v>
       </c>
@@ -38620,7 +38958,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="756" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>726</v>
       </c>
@@ -38661,7 +38999,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="757" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>726</v>
       </c>
@@ -38702,7 +39040,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="758" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>726</v>
       </c>
@@ -38743,7 +39081,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="759" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>726</v>
       </c>
@@ -38784,7 +39122,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="760" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>726</v>
       </c>
@@ -38825,7 +39163,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="761" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>726</v>
       </c>
@@ -38860,7 +39198,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="762" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>726</v>
       </c>
@@ -38898,7 +39236,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="763" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>726</v>
       </c>
@@ -38936,7 +39274,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="764" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>726</v>
       </c>
@@ -38974,7 +39312,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="765" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>726</v>
       </c>
@@ -39006,7 +39344,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="766" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>726</v>
       </c>
@@ -39044,7 +39382,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="767" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>726</v>
       </c>
@@ -40224,8 +40562,22 @@
         <v>446</v>
       </c>
     </row>
+    <row r="803" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A803" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B803" t="s">
+        <v>1047</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AP802" xr:uid="{93A70181-B22C-4671-9C22-4B8DA5FE66AB}"/>
+  <autoFilter ref="A1:AP803" xr:uid="{93A70181-B22C-4671-9C22-4B8DA5FE66AB}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="bugs"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="C677:C724">
     <cfRule type="cellIs" dxfId="123" priority="16" operator="equal">
@@ -40233,69 +40585,69 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D560">
-    <cfRule type="cellIs" dxfId="122" priority="123" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="124" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="121" priority="123" operator="equal">
       <formula>"NA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="124" operator="equal">
-      <formula>""</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="120" priority="125" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D562:D563 D568:D569 D571:D575 D577 D579:D581 D583 D586 D588:D590 D607:D608 D613 D627:D628 D655:D656 D659 D663:D665 D667">
-    <cfRule type="cellIs" dxfId="119" priority="97" operator="equal">
-      <formula>"NA"</formula>
+    <cfRule type="cellIs" dxfId="119" priority="99" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="118" priority="98" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="99" operator="equal">
-      <formula>"Increase"</formula>
+    <cfRule type="cellIs" dxfId="117" priority="97" operator="equal">
+      <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D596:D598 D604">
-    <cfRule type="cellIs" dxfId="116" priority="85" operator="equal">
-      <formula>"NA"</formula>
+    <cfRule type="cellIs" dxfId="116" priority="87" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="115" priority="86" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="87" operator="equal">
-      <formula>"Increase"</formula>
+    <cfRule type="cellIs" dxfId="114" priority="85" operator="equal">
+      <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D617:D618 D623">
-    <cfRule type="cellIs" dxfId="113" priority="82" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="83" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="112" priority="82" operator="equal">
       <formula>"NA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="83" operator="equal">
-      <formula>""</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="111" priority="84" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D637:D638">
-    <cfRule type="cellIs" dxfId="110" priority="79" operator="equal">
-      <formula>"NA"</formula>
+    <cfRule type="cellIs" dxfId="110" priority="81" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="109" priority="80" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="81" operator="equal">
-      <formula>"Increase"</formula>
+    <cfRule type="cellIs" dxfId="108" priority="79" operator="equal">
+      <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D647:D648">
-    <cfRule type="cellIs" dxfId="107" priority="76" operator="equal">
-      <formula>"NA"</formula>
+    <cfRule type="cellIs" dxfId="107" priority="78" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="106" priority="77" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="78" operator="equal">
-      <formula>"Increase"</formula>
+    <cfRule type="cellIs" dxfId="105" priority="76" operator="equal">
+      <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D670:D682">
@@ -40310,36 +40662,36 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D684">
-    <cfRule type="cellIs" dxfId="101" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="33" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="100" priority="31" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="32" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="33" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D686">
-    <cfRule type="cellIs" dxfId="98" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="36" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="97" priority="34" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="35" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="36" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D691:D694">
-    <cfRule type="cellIs" dxfId="95" priority="37" operator="equal">
-      <formula>"NA"</formula>
+    <cfRule type="cellIs" dxfId="95" priority="39" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="94" priority="38" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="39" operator="equal">
-      <formula>"Increase"</formula>
+    <cfRule type="cellIs" dxfId="93" priority="37" operator="equal">
+      <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D697">
@@ -40354,14 +40706,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D706:D707">
-    <cfRule type="cellIs" dxfId="89" priority="22" operator="equal">
-      <formula>"NA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="23" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="24" operator="equal">
       <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="87" priority="22" operator="equal">
+      <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D714:D716">
@@ -40379,11 +40731,11 @@
     <cfRule type="cellIs" dxfId="83" priority="46" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="48" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="81" priority="47" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="48" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D726:D727">
@@ -40398,36 +40750,36 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D730:D731">
-    <cfRule type="cellIs" dxfId="77" priority="56" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="58" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="56" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="57" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="58" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D733">
-    <cfRule type="cellIs" dxfId="74" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="54" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="53" operator="equal">
       <formula>"NA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="54" operator="equal">
-      <formula>""</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="72" priority="55" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D735:D802">
-    <cfRule type="cellIs" dxfId="71" priority="1" operator="equal">
-      <formula>"NA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="2" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="3" operator="equal">
       <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="69" priority="1" operator="equal">
+      <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E197:E202 E214 E226:F226 E238:F238 E250:F250">
@@ -40447,19 +40799,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E401 E413 E425 E437:F437 E449:F449">
-    <cfRule type="cellIs" dxfId="64" priority="274" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="275" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="274" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="275" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E407:E410">
-    <cfRule type="cellIs" dxfId="62" priority="206" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="207" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="206" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="207" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E415 E418">
@@ -40471,27 +40823,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E427">
-    <cfRule type="cellIs" dxfId="58" priority="228" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="229" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="57" priority="228" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="229" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E430">
-    <cfRule type="cellIs" dxfId="56" priority="183" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="184" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="55" priority="183" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="184" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E262:F263 F264">
-    <cfRule type="cellIs" dxfId="54" priority="426" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="427" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="53" priority="426" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="427" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E269:F269 F270">
@@ -40503,19 +40855,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E403:F403">
-    <cfRule type="cellIs" dxfId="50" priority="194" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="195" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="194" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="195" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E461:F463">
-    <cfRule type="cellIs" dxfId="48" priority="226" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="227" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="47" priority="226" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="227" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E468:F469">
@@ -40527,19 +40879,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F191 E192:F192">
-    <cfRule type="cellIs" dxfId="44" priority="521" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="522" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="521" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="522" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F193:F214">
-    <cfRule type="cellIs" dxfId="42" priority="451" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="452" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="41" priority="451" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="452" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F236">
@@ -40551,27 +40903,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F260">
-    <cfRule type="cellIs" dxfId="38" priority="457" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="458" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="457" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="458" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F390 E391:F391 E396:E399">
-    <cfRule type="cellIs" dxfId="36" priority="333" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="334" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="35" priority="333" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="334" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F392:F402">
-    <cfRule type="cellIs" dxfId="34" priority="200" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="201" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="200" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="201" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F404:F414">
@@ -40599,11 +40951,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F459">
-    <cfRule type="cellIs" dxfId="26" priority="290" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="291" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="290" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="291" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H191:H274">
@@ -40644,11 +40996,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O411 O435 O459">
-    <cfRule type="cellIs" dxfId="15" priority="280" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="281" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="280" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="281" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O174:P192 O390:P391">
@@ -40724,10 +41076,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{544F088F-E018-4AF1-A817-C6B9859D0A47}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:Z110"/>
+  <dimension ref="A1:Z122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
@@ -41261,7 +41613,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>526</v>
       </c>
@@ -41323,7 +41675,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>526</v>
       </c>
@@ -41385,7 +41737,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>527</v>
       </c>
@@ -41441,7 +41793,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>292</v>
       </c>
@@ -41491,7 +41843,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>292</v>
       </c>
@@ -41541,7 +41893,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>292</v>
       </c>
@@ -41591,7 +41943,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>292</v>
       </c>
@@ -41641,7 +41993,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>294</v>
       </c>
@@ -41709,7 +42061,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>294</v>
       </c>
@@ -41777,7 +42129,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>294</v>
       </c>
@@ -41845,7 +42197,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>295</v>
       </c>
@@ -41901,7 +42253,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>295</v>
       </c>
@@ -41957,7 +42309,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>295</v>
       </c>
@@ -42013,7 +42365,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>295</v>
       </c>
@@ -42069,7 +42421,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>295</v>
       </c>
@@ -42125,7 +42477,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>295</v>
       </c>
@@ -42181,7 +42533,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>295</v>
       </c>
@@ -42237,7 +42589,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>295</v>
       </c>
@@ -42293,7 +42645,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>295</v>
       </c>
@@ -42349,7 +42701,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>295</v>
       </c>
@@ -42399,7 +42751,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>506</v>
       </c>
@@ -42461,7 +42813,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>506</v>
       </c>
@@ -42523,7 +42875,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>506</v>
       </c>
@@ -42585,7 +42937,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>506</v>
       </c>
@@ -42647,7 +42999,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>506</v>
       </c>
@@ -42709,7 +43061,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>503</v>
       </c>
@@ -42753,7 +43105,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>272</v>
       </c>
@@ -42809,7 +43161,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>272</v>
       </c>
@@ -42865,7 +43217,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>272</v>
       </c>
@@ -42921,7 +43273,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>272</v>
       </c>
@@ -42977,7 +43329,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>300</v>
       </c>
@@ -43045,7 +43397,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>300</v>
       </c>
@@ -43113,7 +43465,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>300</v>
       </c>
@@ -43181,7 +43533,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>300</v>
       </c>
@@ -43249,7 +43601,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>300</v>
       </c>
@@ -43317,7 +43669,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>300</v>
       </c>
@@ -43385,7 +43737,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>389</v>
       </c>
@@ -43429,7 +43781,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>389</v>
       </c>
@@ -43473,7 +43825,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>394</v>
       </c>
@@ -43535,7 +43887,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>394</v>
       </c>
@@ -43597,7 +43949,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>394</v>
       </c>
@@ -43659,7 +44011,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>394</v>
       </c>
@@ -43721,7 +44073,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>394</v>
       </c>
@@ -43783,7 +44135,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>394</v>
       </c>
@@ -43845,7 +44197,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>394</v>
       </c>
@@ -43907,7 +44259,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>417</v>
       </c>
@@ -43969,7 +44321,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>417</v>
       </c>
@@ -44031,7 +44383,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>417</v>
       </c>
@@ -44093,7 +44445,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>417</v>
       </c>
@@ -44155,7 +44507,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>417</v>
       </c>
@@ -44217,7 +44569,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>417</v>
       </c>
@@ -44279,7 +44631,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>417</v>
       </c>
@@ -44341,7 +44693,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>479</v>
       </c>
@@ -44409,7 +44761,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>479</v>
       </c>
@@ -44477,7 +44829,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>479</v>
       </c>
@@ -44545,7 +44897,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>479</v>
       </c>
@@ -44613,7 +44965,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>479</v>
       </c>
@@ -44681,7 +45033,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>479</v>
       </c>
@@ -44749,7 +45101,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>542</v>
       </c>
@@ -44820,7 +45172,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>542</v>
       </c>
@@ -44891,7 +45243,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>542</v>
       </c>
@@ -44962,7 +45314,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>563</v>
       </c>
@@ -45024,7 +45376,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>563</v>
       </c>
@@ -45086,7 +45438,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>563</v>
       </c>
@@ -45148,7 +45500,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>584</v>
       </c>
@@ -45210,7 +45562,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>602</v>
       </c>
@@ -45272,7 +45624,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>602</v>
       </c>
@@ -45334,7 +45686,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>643</v>
       </c>
@@ -45396,7 +45748,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>657</v>
       </c>
@@ -45458,7 +45810,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>658</v>
       </c>
@@ -45520,7 +45872,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>659</v>
       </c>
@@ -45588,7 +45940,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>669</v>
       </c>
@@ -45632,7 +45984,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>669</v>
       </c>
@@ -45676,7 +46028,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>669</v>
       </c>
@@ -45720,7 +46072,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>701</v>
       </c>
@@ -45776,7 +46128,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>701</v>
       </c>
@@ -45832,7 +46184,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>701</v>
       </c>
@@ -45888,7 +46240,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>673</v>
       </c>
@@ -45959,7 +46311,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>673</v>
       </c>
@@ -46030,7 +46382,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>673</v>
       </c>
@@ -46101,7 +46453,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>673</v>
       </c>
@@ -46172,7 +46524,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>673</v>
       </c>
@@ -46243,7 +46595,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>673</v>
       </c>
@@ -46314,7 +46666,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>673</v>
       </c>
@@ -46385,7 +46737,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>673</v>
       </c>
@@ -46456,7 +46808,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>673</v>
       </c>
@@ -46527,7 +46879,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>726</v>
       </c>
@@ -46598,7 +46950,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>726</v>
       </c>
@@ -46669,7 +47021,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>726</v>
       </c>
@@ -46740,7 +47092,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>726</v>
       </c>
@@ -46811,7 +47163,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>726</v>
       </c>
@@ -46882,7 +47234,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>726</v>
       </c>
@@ -46953,7 +47305,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>726</v>
       </c>
@@ -47024,7 +47376,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>726</v>
       </c>
@@ -47095,7 +47447,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>726</v>
       </c>
@@ -47166,7 +47518,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>998</v>
       </c>
@@ -47176,7 +47528,7 @@
       <c r="C104" t="s">
         <v>100</v>
       </c>
-      <c r="D104" s="33">
+      <c r="D104">
         <v>6</v>
       </c>
       <c r="E104" t="s">
@@ -47228,7 +47580,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>998</v>
       </c>
@@ -47238,7 +47590,7 @@
       <c r="C105" t="s">
         <v>100</v>
       </c>
-      <c r="D105" s="33">
+      <c r="D105">
         <v>4</v>
       </c>
       <c r="E105" t="s">
@@ -47290,7 +47642,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>998</v>
       </c>
@@ -47300,7 +47652,7 @@
       <c r="C106" t="s">
         <v>100</v>
       </c>
-      <c r="D106" s="33">
+      <c r="D106">
         <v>6</v>
       </c>
       <c r="E106" t="s">
@@ -47352,7 +47704,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>998</v>
       </c>
@@ -47362,7 +47714,7 @@
       <c r="C107" t="s">
         <v>100</v>
       </c>
-      <c r="D107" s="33">
+      <c r="D107">
         <v>5</v>
       </c>
       <c r="E107" t="s">
@@ -47414,7 +47766,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>998</v>
       </c>
@@ -47424,7 +47776,7 @@
       <c r="C108" t="s">
         <v>100</v>
       </c>
-      <c r="D108" s="33">
+      <c r="D108">
         <v>4</v>
       </c>
       <c r="E108" t="s">
@@ -47476,7 +47828,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>998</v>
       </c>
@@ -47486,7 +47838,7 @@
       <c r="C109" t="s">
         <v>100</v>
       </c>
-      <c r="D109" s="33">
+      <c r="D109">
         <v>5</v>
       </c>
       <c r="E109" t="s">
@@ -47538,7 +47890,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="110" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>998</v>
       </c>
@@ -47548,7 +47900,7 @@
       <c r="C110" t="s">
         <v>100</v>
       </c>
-      <c r="D110" s="33">
+      <c r="D110">
         <v>5</v>
       </c>
       <c r="E110" t="s">
@@ -47600,8 +47952,685 @@
         <v>446</v>
       </c>
     </row>
+    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C111" t="s">
+        <v>100</v>
+      </c>
+      <c r="D111">
+        <v>4</v>
+      </c>
+      <c r="E111" t="s">
+        <v>106</v>
+      </c>
+      <c r="G111" t="s">
+        <v>99</v>
+      </c>
+      <c r="H111">
+        <v>4</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+      <c r="J111">
+        <v>2</v>
+      </c>
+      <c r="K111">
+        <v>2.65</v>
+      </c>
+      <c r="L111">
+        <v>3</v>
+      </c>
+      <c r="M111">
+        <v>5</v>
+      </c>
+      <c r="P111" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>407</v>
+      </c>
+      <c r="R111" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S111" t="s">
+        <v>1049</v>
+      </c>
+      <c r="V111" t="b">
+        <v>0</v>
+      </c>
+      <c r="W111" t="s">
+        <v>78</v>
+      </c>
+      <c r="X111" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y111" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C112" t="s">
+        <v>100</v>
+      </c>
+      <c r="D112">
+        <v>6</v>
+      </c>
+      <c r="E112" t="s">
+        <v>106</v>
+      </c>
+      <c r="G112" t="s">
+        <v>99</v>
+      </c>
+      <c r="H112">
+        <v>4</v>
+      </c>
+      <c r="I112">
+        <v>1</v>
+      </c>
+      <c r="J112">
+        <v>2</v>
+      </c>
+      <c r="K112">
+        <v>2.65</v>
+      </c>
+      <c r="L112">
+        <v>3</v>
+      </c>
+      <c r="M112">
+        <v>5</v>
+      </c>
+      <c r="P112" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>407</v>
+      </c>
+      <c r="R112" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S112" t="s">
+        <v>1049</v>
+      </c>
+      <c r="V112" t="b">
+        <v>0</v>
+      </c>
+      <c r="W112" t="s">
+        <v>78</v>
+      </c>
+      <c r="X112" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y112" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C113" t="s">
+        <v>100</v>
+      </c>
+      <c r="D113">
+        <v>6</v>
+      </c>
+      <c r="E113" t="s">
+        <v>106</v>
+      </c>
+      <c r="G113" t="s">
+        <v>99</v>
+      </c>
+      <c r="H113">
+        <v>4</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+      <c r="J113">
+        <v>2</v>
+      </c>
+      <c r="K113">
+        <v>2.65</v>
+      </c>
+      <c r="L113">
+        <v>3</v>
+      </c>
+      <c r="M113">
+        <v>5</v>
+      </c>
+      <c r="P113" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>407</v>
+      </c>
+      <c r="R113" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S113" t="s">
+        <v>1049</v>
+      </c>
+      <c r="V113" t="b">
+        <v>0</v>
+      </c>
+      <c r="W113" t="s">
+        <v>78</v>
+      </c>
+      <c r="X113" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C114" t="s">
+        <v>100</v>
+      </c>
+      <c r="D114">
+        <v>6</v>
+      </c>
+      <c r="E114" t="s">
+        <v>106</v>
+      </c>
+      <c r="G114" t="s">
+        <v>99</v>
+      </c>
+      <c r="H114">
+        <v>4</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="J114">
+        <v>2</v>
+      </c>
+      <c r="K114">
+        <v>2.65</v>
+      </c>
+      <c r="L114">
+        <v>3</v>
+      </c>
+      <c r="M114">
+        <v>5</v>
+      </c>
+      <c r="P114" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>407</v>
+      </c>
+      <c r="R114" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S114" t="s">
+        <v>1049</v>
+      </c>
+      <c r="V114" t="b">
+        <v>0</v>
+      </c>
+      <c r="W114" t="s">
+        <v>78</v>
+      </c>
+      <c r="X114" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y114" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C115" t="s">
+        <v>100</v>
+      </c>
+      <c r="D115">
+        <v>7</v>
+      </c>
+      <c r="E115" t="s">
+        <v>106</v>
+      </c>
+      <c r="G115" t="s">
+        <v>99</v>
+      </c>
+      <c r="H115">
+        <v>4</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="J115">
+        <v>2</v>
+      </c>
+      <c r="K115">
+        <v>2.65</v>
+      </c>
+      <c r="L115">
+        <v>3</v>
+      </c>
+      <c r="M115">
+        <v>5</v>
+      </c>
+      <c r="P115" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>407</v>
+      </c>
+      <c r="R115" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S115" t="s">
+        <v>1049</v>
+      </c>
+      <c r="V115" t="b">
+        <v>0</v>
+      </c>
+      <c r="W115" t="s">
+        <v>78</v>
+      </c>
+      <c r="X115" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y115" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C116" t="s">
+        <v>100</v>
+      </c>
+      <c r="D116">
+        <v>6</v>
+      </c>
+      <c r="E116" t="s">
+        <v>106</v>
+      </c>
+      <c r="G116" t="s">
+        <v>99</v>
+      </c>
+      <c r="H116">
+        <v>4</v>
+      </c>
+      <c r="I116">
+        <v>1</v>
+      </c>
+      <c r="J116">
+        <v>2</v>
+      </c>
+      <c r="K116">
+        <v>2.65</v>
+      </c>
+      <c r="L116">
+        <v>3</v>
+      </c>
+      <c r="M116">
+        <v>5</v>
+      </c>
+      <c r="P116" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>407</v>
+      </c>
+      <c r="R116" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S116" t="s">
+        <v>1049</v>
+      </c>
+      <c r="V116" t="b">
+        <v>0</v>
+      </c>
+      <c r="W116" t="s">
+        <v>78</v>
+      </c>
+      <c r="X116" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y116" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C117" t="s">
+        <v>100</v>
+      </c>
+      <c r="D117">
+        <v>7</v>
+      </c>
+      <c r="E117" t="s">
+        <v>106</v>
+      </c>
+      <c r="G117" t="s">
+        <v>99</v>
+      </c>
+      <c r="H117">
+        <v>4</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117">
+        <v>2</v>
+      </c>
+      <c r="K117">
+        <v>2.65</v>
+      </c>
+      <c r="L117">
+        <v>3</v>
+      </c>
+      <c r="M117">
+        <v>5</v>
+      </c>
+      <c r="P117" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>407</v>
+      </c>
+      <c r="R117" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S117" t="s">
+        <v>1049</v>
+      </c>
+      <c r="V117" t="b">
+        <v>0</v>
+      </c>
+      <c r="W117" t="s">
+        <v>78</v>
+      </c>
+      <c r="X117" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y117" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C118" t="s">
+        <v>100</v>
+      </c>
+      <c r="E118" t="s">
+        <v>106</v>
+      </c>
+      <c r="G118" t="s">
+        <v>99</v>
+      </c>
+      <c r="H118">
+        <v>4</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="J118">
+        <v>2</v>
+      </c>
+      <c r="K118">
+        <v>2.65</v>
+      </c>
+      <c r="L118">
+        <v>3</v>
+      </c>
+      <c r="M118">
+        <v>5</v>
+      </c>
+      <c r="P118" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>407</v>
+      </c>
+      <c r="R118" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S118" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C119" t="s">
+        <v>100</v>
+      </c>
+      <c r="E119" t="s">
+        <v>106</v>
+      </c>
+      <c r="G119" t="s">
+        <v>99</v>
+      </c>
+      <c r="H119">
+        <v>4</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="J119">
+        <v>2</v>
+      </c>
+      <c r="K119">
+        <v>2.65</v>
+      </c>
+      <c r="L119">
+        <v>3</v>
+      </c>
+      <c r="M119">
+        <v>5</v>
+      </c>
+      <c r="P119" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>407</v>
+      </c>
+      <c r="R119" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S119" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C120" t="s">
+        <v>100</v>
+      </c>
+      <c r="E120" t="s">
+        <v>106</v>
+      </c>
+      <c r="G120" t="s">
+        <v>99</v>
+      </c>
+      <c r="H120">
+        <v>4</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
+      </c>
+      <c r="J120">
+        <v>2</v>
+      </c>
+      <c r="K120">
+        <v>2.65</v>
+      </c>
+      <c r="L120">
+        <v>3</v>
+      </c>
+      <c r="M120">
+        <v>5</v>
+      </c>
+      <c r="P120" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>407</v>
+      </c>
+      <c r="R120" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S120" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C121" t="s">
+        <v>100</v>
+      </c>
+      <c r="E121" t="s">
+        <v>106</v>
+      </c>
+      <c r="G121" t="s">
+        <v>99</v>
+      </c>
+      <c r="H121">
+        <v>4</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+      <c r="J121">
+        <v>2</v>
+      </c>
+      <c r="K121">
+        <v>2.65</v>
+      </c>
+      <c r="L121">
+        <v>3</v>
+      </c>
+      <c r="M121">
+        <v>5</v>
+      </c>
+      <c r="P121" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>407</v>
+      </c>
+      <c r="R121" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S121" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C122" t="s">
+        <v>100</v>
+      </c>
+      <c r="E122" t="s">
+        <v>106</v>
+      </c>
+      <c r="G122" t="s">
+        <v>99</v>
+      </c>
+      <c r="H122">
+        <v>4</v>
+      </c>
+      <c r="I122">
+        <v>1</v>
+      </c>
+      <c r="J122">
+        <v>2</v>
+      </c>
+      <c r="K122">
+        <v>2.65</v>
+      </c>
+      <c r="L122">
+        <v>3</v>
+      </c>
+      <c r="M122">
+        <v>5</v>
+      </c>
+      <c r="P122" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>407</v>
+      </c>
+      <c r="R122" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S122" t="s">
+        <v>1049</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z103" xr:uid="{544F088F-E018-4AF1-A817-C6B9859D0A47}"/>
+  <autoFilter ref="A1:Z117" xr:uid="{544F088F-E018-4AF1-A817-C6B9859D0A47}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="ChesBay_2002"/>
+        <filter val="MBSS_2005_Bugs"/>
+        <filter val="MBSS_2005_Fish"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -47610,7 +48639,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BB61F63-921C-4D79-B43A-73F58D6664BB}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
@@ -47650,7 +48679,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="str" cm="1">
-        <f t="array" ref="A4:A29">_xlfn.UNIQUE(metric.scoring!A2:A988)</f>
+        <f t="array" ref="A4:A30">_xlfn.UNIQUE(metric.scoring!A2:A988)</f>
         <v>MBSS_2005_Bugs</v>
       </c>
       <c r="B4" cm="1">
@@ -48075,7 +49104,12 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29">
+      <c r="A29" t="str">
+        <v>ChesBay_2002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
         <v>0</v>
       </c>
     </row>
@@ -48363,7 +49397,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11763AB-DE5A-4277-BE65-88CD3BDAAE84}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
@@ -48558,6 +49592,17 @@
         <v>751</v>
       </c>
     </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>1046</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C15" r:id="rId1" display="http://files.dep.state.pa.us/Water/Drinking Water and Facility Regulation/WaterQualityPortalFiles/Technical Documentation/freestoneIBImarch2012.pdf" xr:uid="{8DDF3760-F620-49EC-AB3A-0D29539F888A}"/>
@@ -48567,6 +49612,7 @@
     <hyperlink ref="K29" r:id="rId5" xr:uid="{8A209776-3F90-4583-8B3C-C1871715ABE5}"/>
     <hyperlink ref="K31" r:id="rId6" xr:uid="{7DA3D426-349D-4A03-9038-96364F0D7EF0}"/>
     <hyperlink ref="D31" r:id="rId7" xr:uid="{9BDA1969-E579-4311-A787-B2F511D14E7B}"/>
+    <hyperlink ref="D32" r:id="rId8" xr:uid="{97DD81E5-0499-4525-82FD-A0762A46B52A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/inst/extdata/MetricScoring.xlsx
+++ b/inst/extdata/MetricScoring.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BioMonTools\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E6F5AA-8209-4110-A159-54C71F9FEC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439B85E7-114D-4CEC-A750-48E064B181C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="ToDo_index" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">index.scoring!$A$1:$Z$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">index.scoring!$A$1:$Z$110</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">metric.scoring!$A$1:$AP$803</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ScoringRegimes!$A$5:$C$17</definedName>
     <definedName name="FileName">NOTES!$B$8</definedName>
@@ -1644,7 +1644,17 @@
         </r>
       </text>
     </comment>
-    <comment ref="K111" authorId="0" shapeId="0" xr:uid="{95AD45BA-D71F-4A27-92ED-EF9216D767C8}">
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Leppo, Erik</author>
+  </authors>
+  <commentList>
+    <comment ref="K17" authorId="0" shapeId="0" xr:uid="{7E07AC98-6E01-4785-A924-16F42C5FB267}">
       <text>
         <r>
           <rPr>
@@ -1668,7 +1678,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K112" authorId="0" shapeId="0" xr:uid="{70C9F623-0A0C-4C1F-A620-B502F0E68E36}">
+    <comment ref="K18" authorId="0" shapeId="0" xr:uid="{FDD6C9FB-F6B4-4714-A0DD-B79A984E4EF2}">
       <text>
         <r>
           <rPr>
@@ -1692,7 +1702,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K113" authorId="0" shapeId="0" xr:uid="{7E1C6060-B64A-4EC4-A2B0-D6C9738C0A85}">
+    <comment ref="K19" authorId="0" shapeId="0" xr:uid="{C8E96C05-0541-4CC4-81AA-A79F5A1B77D2}">
       <text>
         <r>
           <rPr>
@@ -1716,7 +1726,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K114" authorId="0" shapeId="0" xr:uid="{3B1DD8B9-AD68-4930-9BF3-88BA6D460296}">
+    <comment ref="K20" authorId="0" shapeId="0" xr:uid="{AACE516E-7079-461D-834C-15633E336260}">
       <text>
         <r>
           <rPr>
@@ -1740,7 +1750,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K115" authorId="0" shapeId="0" xr:uid="{541693CE-2BA1-431A-A4E0-052062F929D7}">
+    <comment ref="K21" authorId="0" shapeId="0" xr:uid="{5E0485B7-9048-4559-A41A-E1940C9D11E6}">
       <text>
         <r>
           <rPr>
@@ -1764,7 +1774,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K116" authorId="0" shapeId="0" xr:uid="{56BFE27A-1311-46ED-81B3-CE7FA43CCDB5}">
+    <comment ref="K22" authorId="0" shapeId="0" xr:uid="{C5DB3849-4EA6-4D22-AAAE-20E74EDDCD56}">
       <text>
         <r>
           <rPr>
@@ -1788,7 +1798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K117" authorId="0" shapeId="0" xr:uid="{F953B359-6421-4FB3-B5CB-337BACC1AD44}">
+    <comment ref="K23" authorId="0" shapeId="0" xr:uid="{B96BA34E-F2AC-414F-8B64-EA900AFD95A4}">
       <text>
         <r>
           <rPr>
@@ -1812,7 +1822,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K118" authorId="0" shapeId="0" xr:uid="{D5E8C9B5-16AA-436E-A6E3-1413ADF84065}">
+    <comment ref="K24" authorId="0" shapeId="0" xr:uid="{7BEE1858-3EFC-4185-846D-280ED1ECB9DD}">
       <text>
         <r>
           <rPr>
@@ -1836,7 +1846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K119" authorId="0" shapeId="0" xr:uid="{09A1E68C-6ED8-4820-9949-F2EB8E605EAD}">
+    <comment ref="K25" authorId="0" shapeId="0" xr:uid="{ACA5F4A7-03F7-4E78-BD91-7475FAB12D7C}">
       <text>
         <r>
           <rPr>
@@ -1860,7 +1870,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K120" authorId="0" shapeId="0" xr:uid="{0D80A14D-063C-4E28-A3A6-746806DF5550}">
+    <comment ref="K26" authorId="0" shapeId="0" xr:uid="{25248764-8948-4C92-A290-8C7FEC1C726B}">
       <text>
         <r>
           <rPr>
@@ -1884,7 +1894,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K121" authorId="0" shapeId="0" xr:uid="{4FF0FCE1-6A7E-436F-887E-888BA5328EFA}">
+    <comment ref="K27" authorId="0" shapeId="0" xr:uid="{E3B6B7F4-FB38-4014-83B6-0BED21975752}">
       <text>
         <r>
           <rPr>
@@ -1908,7 +1918,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K122" authorId="0" shapeId="0" xr:uid="{CFF85006-E8A3-4BDC-AF4D-97573717BF42}">
+    <comment ref="K28" authorId="0" shapeId="0" xr:uid="{359B4092-73D7-4B26-AB79-AD74DF6F4123}">
       <text>
         <r>
           <rPr>
@@ -1959,7 +1969,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10092" uniqueCount="1061">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10118" uniqueCount="1063">
   <si>
     <t>Erik.Leppo@tetratech.com</t>
   </si>
@@ -5142,6 +5152,12 @@
   </si>
   <si>
     <t>PO_mud_biomass</t>
+  </si>
+  <si>
+    <t>Chesapeake Bay</t>
+  </si>
+  <si>
+    <t>Chesapeake Bay BIBI to "to do" section</t>
   </si>
 </sst>
 </file>
@@ -5420,7 +5436,7 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3"/>
@@ -5466,6 +5482,7 @@
     <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Bad" xfId="6" builtinId="27"/>
@@ -5482,6 +5499,16 @@
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5637,16 +5664,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color auto="1"/>
       </font>
       <fill>
@@ -5727,21 +5744,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color auto="1"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5807,201 +5824,11 @@
     </dxf>
     <dxf>
       <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6067,21 +5894,21 @@
     </dxf>
     <dxf>
       <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6127,231 +5954,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color auto="1"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6397,21 +6004,171 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
+        <color auto="1"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6497,6 +6254,26 @@
     </dxf>
     <dxf>
       <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -6527,81 +6304,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6627,11 +6334,31 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color auto="1"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6647,11 +6374,31 @@
     </dxf>
     <dxf>
       <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6667,11 +6414,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6687,6 +6434,16 @@
     </dxf>
     <dxf>
       <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -6697,11 +6454,271 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color auto="1"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7055,7 +7072,7 @@
   <sheetPr codeName="sh_Notes">
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -7090,7 +7107,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>46006</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7860,6 +7877,14 @@
       </c>
       <c r="B111" t="s">
         <v>997</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="5">
+        <v>46160</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1062</v>
       </c>
     </row>
   </sheetData>
@@ -7887,10 +7912,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A70181-B22C-4671-9C22-4B8DA5FE66AB}">
-  <sheetPr codeName="Sheet1" filterMode="1">
+  <sheetPr codeName="Sheet1">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:AP803"/>
+  <dimension ref="A1:AP802"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" customWidth="1"/>
@@ -8734,7 +8759,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>525</v>
       </c>
@@ -8766,7 +8791,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>525</v>
       </c>
@@ -8798,7 +8823,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>525</v>
       </c>
@@ -8830,7 +8855,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>525</v>
       </c>
@@ -8862,7 +8887,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>525</v>
       </c>
@@ -8894,7 +8919,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>525</v>
       </c>
@@ -8926,7 +8951,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>525</v>
       </c>
@@ -8958,7 +8983,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>525</v>
       </c>
@@ -8990,7 +9015,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>525</v>
       </c>
@@ -9022,7 +9047,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>525</v>
       </c>
@@ -9054,7 +9079,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>525</v>
       </c>
@@ -9086,7 +9111,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>525</v>
       </c>
@@ -9118,7 +9143,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>525</v>
       </c>
@@ -9150,7 +9175,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>525</v>
       </c>
@@ -9182,7 +9207,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>525</v>
       </c>
@@ -9214,7 +9239,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>525</v>
       </c>
@@ -9246,7 +9271,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>525</v>
       </c>
@@ -9278,7 +9303,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>525</v>
       </c>
@@ -9310,7 +9335,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>525</v>
       </c>
@@ -9342,7 +9367,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>525</v>
       </c>
@@ -9374,7 +9399,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>525</v>
       </c>
@@ -9406,7 +9431,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>525</v>
       </c>
@@ -13935,7 +13960,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="191" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>300</v>
       </c>
@@ -14000,7 +14025,7 @@
         <v>11.86</v>
       </c>
     </row>
-    <row r="192" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>300</v>
       </c>
@@ -14068,7 +14093,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="193" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>300</v>
       </c>
@@ -14133,7 +14158,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="194" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>300</v>
       </c>
@@ -14198,7 +14223,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="195" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>300</v>
       </c>
@@ -14263,7 +14288,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="196" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>300</v>
       </c>
@@ -14328,7 +14353,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="197" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>300</v>
       </c>
@@ -14387,7 +14412,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="198" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>300</v>
       </c>
@@ -14464,7 +14489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>300</v>
       </c>
@@ -14529,7 +14554,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="200" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>300</v>
       </c>
@@ -14594,7 +14619,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="201" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>300</v>
       </c>
@@ -14659,7 +14684,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="202" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>300</v>
       </c>
@@ -14724,7 +14749,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="203" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>300</v>
       </c>
@@ -14789,7 +14814,7 @@
         <v>11.86</v>
       </c>
     </row>
-    <row r="204" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>300</v>
       </c>
@@ -14857,7 +14882,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="205" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>300</v>
       </c>
@@ -14925,7 +14950,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="206" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>300</v>
       </c>
@@ -14990,7 +15015,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="207" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>300</v>
       </c>
@@ -15055,7 +15080,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="208" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>300</v>
       </c>
@@ -15123,7 +15148,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="209" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>300</v>
       </c>
@@ -15188,7 +15213,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="210" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>300</v>
       </c>
@@ -15265,7 +15290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>300</v>
       </c>
@@ -15330,7 +15355,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="212" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>300</v>
       </c>
@@ -15395,7 +15420,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="213" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>300</v>
       </c>
@@ -15460,7 +15485,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="214" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>300</v>
       </c>
@@ -15525,7 +15550,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="215" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>300</v>
       </c>
@@ -15590,7 +15615,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="216" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>300</v>
       </c>
@@ -15658,7 +15683,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="217" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>300</v>
       </c>
@@ -15723,7 +15748,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="218" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>300</v>
       </c>
@@ -15790,7 +15815,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="219" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>300</v>
       </c>
@@ -15858,7 +15883,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="220" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>300</v>
       </c>
@@ -15923,7 +15948,7 @@
         <v>3.06</v>
       </c>
     </row>
-    <row r="221" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>300</v>
       </c>
@@ -15988,7 +16013,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="222" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>300</v>
       </c>
@@ -16065,7 +16090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>300</v>
       </c>
@@ -16130,7 +16155,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="224" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>300</v>
       </c>
@@ -16195,7 +16220,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="225" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>300</v>
       </c>
@@ -16260,7 +16285,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="226" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>300</v>
       </c>
@@ -16325,7 +16350,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="227" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>300</v>
       </c>
@@ -16390,7 +16415,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="228" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>300</v>
       </c>
@@ -16458,7 +16483,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="229" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>300</v>
       </c>
@@ -16526,7 +16551,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="230" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>300</v>
       </c>
@@ -16593,7 +16618,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="231" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>300</v>
       </c>
@@ -16661,7 +16686,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="232" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>300</v>
       </c>
@@ -16726,7 +16751,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="233" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>300</v>
       </c>
@@ -16791,7 +16816,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="234" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>300</v>
       </c>
@@ -16868,7 +16893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>300</v>
       </c>
@@ -16933,7 +16958,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="236" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>300</v>
       </c>
@@ -16998,7 +17023,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="237" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>300</v>
       </c>
@@ -17063,7 +17088,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="238" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>300</v>
       </c>
@@ -17128,7 +17153,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="239" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>300</v>
       </c>
@@ -17193,7 +17218,7 @@
         <v>9.66</v>
       </c>
     </row>
-    <row r="240" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>300</v>
       </c>
@@ -17258,7 +17283,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="241" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>300</v>
       </c>
@@ -17323,7 +17348,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="242" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>300</v>
       </c>
@@ -17388,7 +17413,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="243" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>300</v>
       </c>
@@ -17453,7 +17478,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="244" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>300</v>
       </c>
@@ -17518,7 +17543,7 @@
         <v>1.79</v>
       </c>
     </row>
-    <row r="245" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>300</v>
       </c>
@@ -17583,7 +17608,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="246" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>300</v>
       </c>
@@ -17660,7 +17685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>300</v>
       </c>
@@ -17725,7 +17750,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="248" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>300</v>
       </c>
@@ -17790,7 +17815,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="249" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>300</v>
       </c>
@@ -17855,7 +17880,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="250" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>300</v>
       </c>
@@ -17920,7 +17945,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="251" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>300</v>
       </c>
@@ -17985,7 +18010,7 @@
         <v>9.66</v>
       </c>
     </row>
-    <row r="252" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>300</v>
       </c>
@@ -18050,7 +18075,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="253" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>300</v>
       </c>
@@ -18115,7 +18140,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="254" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>300</v>
       </c>
@@ -18180,7 +18205,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="255" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>300</v>
       </c>
@@ -18245,7 +18270,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="256" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>300</v>
       </c>
@@ -18310,7 +18335,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="257" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>300</v>
       </c>
@@ -18375,7 +18400,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="258" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>300</v>
       </c>
@@ -18452,7 +18477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>300</v>
       </c>
@@ -18517,7 +18542,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="260" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>300</v>
       </c>
@@ -18582,7 +18607,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="261" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>300</v>
       </c>
@@ -18647,7 +18672,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="262" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>300</v>
       </c>
@@ -18712,7 +18737,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="263" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>300</v>
       </c>
@@ -18789,7 +18814,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="264" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>300</v>
       </c>
@@ -18866,7 +18891,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="265" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>300</v>
       </c>
@@ -18943,7 +18968,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="266" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>300</v>
       </c>
@@ -19020,7 +19045,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="267" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>300</v>
       </c>
@@ -19097,7 +19122,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="268" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>300</v>
       </c>
@@ -19174,7 +19199,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="269" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>300</v>
       </c>
@@ -19251,7 +19276,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="270" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>300</v>
       </c>
@@ -19328,7 +19353,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="271" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>300</v>
       </c>
@@ -19405,7 +19430,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="272" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>300</v>
       </c>
@@ -19482,7 +19507,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="273" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>300</v>
       </c>
@@ -19559,7 +19584,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="274" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>300</v>
       </c>
@@ -23089,7 +23114,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="390" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>479</v>
       </c>
@@ -23154,7 +23179,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="391" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>479</v>
       </c>
@@ -23219,7 +23244,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="392" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>479</v>
       </c>
@@ -23284,7 +23309,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="393" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>479</v>
       </c>
@@ -23349,7 +23374,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="394" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>479</v>
       </c>
@@ -23414,7 +23439,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="395" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>479</v>
       </c>
@@ -23479,7 +23504,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="396" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>479</v>
       </c>
@@ -23538,7 +23563,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="397" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>479</v>
       </c>
@@ -23615,7 +23640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>479</v>
       </c>
@@ -23680,7 +23705,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="399" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>479</v>
       </c>
@@ -23745,7 +23770,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="400" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>479</v>
       </c>
@@ -23810,7 +23835,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="401" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>479</v>
       </c>
@@ -23875,7 +23900,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="402" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>479</v>
       </c>
@@ -23940,7 +23965,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="403" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>479</v>
       </c>
@@ -24005,7 +24030,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="404" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>479</v>
       </c>
@@ -24070,7 +24095,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="405" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>479</v>
       </c>
@@ -24135,7 +24160,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="406" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>479</v>
       </c>
@@ -24200,7 +24225,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="407" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>479</v>
       </c>
@@ -24265,7 +24290,7 @@
         <v>-0.19</v>
       </c>
     </row>
-    <row r="408" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>479</v>
       </c>
@@ -24330,7 +24355,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="409" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>479</v>
       </c>
@@ -24407,7 +24432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>479</v>
       </c>
@@ -24472,7 +24497,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="411" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>479</v>
       </c>
@@ -24537,7 +24562,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="412" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>479</v>
       </c>
@@ -24602,7 +24627,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="413" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>479</v>
       </c>
@@ -24667,7 +24692,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="414" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>479</v>
       </c>
@@ -24732,7 +24757,7 @@
         <v>8.49</v>
       </c>
     </row>
-    <row r="415" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>479</v>
       </c>
@@ -24797,7 +24822,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="416" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>479</v>
       </c>
@@ -24862,7 +24887,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="417" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>479</v>
       </c>
@@ -24927,7 +24952,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="418" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>479</v>
       </c>
@@ -24992,7 +25017,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="419" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>479</v>
       </c>
@@ -25057,7 +25082,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="420" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>479</v>
       </c>
@@ -25122,7 +25147,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="421" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>479</v>
       </c>
@@ -25199,7 +25224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>479</v>
       </c>
@@ -25264,7 +25289,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="423" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>479</v>
       </c>
@@ -25329,7 +25354,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="424" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>479</v>
       </c>
@@ -25394,7 +25419,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="425" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>479</v>
       </c>
@@ -25459,7 +25484,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="426" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>479</v>
       </c>
@@ -25524,7 +25549,7 @@
         <v>8.49</v>
       </c>
     </row>
-    <row r="427" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>479</v>
       </c>
@@ -25589,7 +25614,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="428" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>479</v>
       </c>
@@ -25654,7 +25679,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="429" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>479</v>
       </c>
@@ -25719,7 +25744,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="430" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>479</v>
       </c>
@@ -25784,7 +25809,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="431" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>479</v>
       </c>
@@ -25849,7 +25874,7 @@
         <v>-0.37</v>
       </c>
     </row>
-    <row r="432" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>479</v>
       </c>
@@ -25914,7 +25939,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="433" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>479</v>
       </c>
@@ -25991,7 +26016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>479</v>
       </c>
@@ -26056,7 +26081,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="435" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>479</v>
       </c>
@@ -26121,7 +26146,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="436" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>479</v>
       </c>
@@ -26186,7 +26211,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="437" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>479</v>
       </c>
@@ -26251,7 +26276,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="438" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>479</v>
       </c>
@@ -26316,7 +26341,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="439" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>479</v>
       </c>
@@ -26381,7 +26406,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="440" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>479</v>
       </c>
@@ -26446,7 +26471,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="441" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>479</v>
       </c>
@@ -26511,7 +26536,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="442" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>479</v>
       </c>
@@ -26576,7 +26601,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="443" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>479</v>
       </c>
@@ -26641,7 +26666,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="444" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>479</v>
       </c>
@@ -26706,7 +26731,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="445" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>479</v>
       </c>
@@ -26783,7 +26808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>479</v>
       </c>
@@ -26848,7 +26873,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="447" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>479</v>
       </c>
@@ -26913,7 +26938,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="448" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>479</v>
       </c>
@@ -26978,7 +27003,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="449" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>479</v>
       </c>
@@ -27043,7 +27068,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="450" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>479</v>
       </c>
@@ -27108,7 +27133,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="451" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>479</v>
       </c>
@@ -27173,7 +27198,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="452" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>479</v>
       </c>
@@ -27238,7 +27263,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="453" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>479</v>
       </c>
@@ -27303,7 +27328,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="454" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>479</v>
       </c>
@@ -27368,7 +27393,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="455" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>479</v>
       </c>
@@ -27433,7 +27458,7 @@
         <v>-0.51</v>
       </c>
     </row>
-    <row r="456" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>479</v>
       </c>
@@ -27498,7 +27523,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="457" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>479</v>
       </c>
@@ -27575,7 +27600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="458" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>479</v>
       </c>
@@ -27640,7 +27665,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="459" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>479</v>
       </c>
@@ -27705,7 +27730,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="460" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>479</v>
       </c>
@@ -27770,7 +27795,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="461" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>479</v>
       </c>
@@ -27835,7 +27860,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="462" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>479</v>
       </c>
@@ -27912,7 +27937,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="463" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>479</v>
       </c>
@@ -27989,7 +28014,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="464" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>479</v>
       </c>
@@ -28066,7 +28091,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="465" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>479</v>
       </c>
@@ -28143,7 +28168,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="466" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>479</v>
       </c>
@@ -28220,7 +28245,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="467" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>479</v>
       </c>
@@ -28297,7 +28322,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="468" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>479</v>
       </c>
@@ -28374,7 +28399,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="469" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>479</v>
       </c>
@@ -28451,7 +28476,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="470" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>479</v>
       </c>
@@ -28528,7 +28553,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="471" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>479</v>
       </c>
@@ -28605,7 +28630,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="472" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>479</v>
       </c>
@@ -28682,7 +28707,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="473" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>479</v>
       </c>
@@ -31454,7 +31479,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="550" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>584</v>
       </c>
@@ -31492,7 +31517,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="551" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>584</v>
       </c>
@@ -31533,7 +31558,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="552" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>584</v>
       </c>
@@ -31574,7 +31599,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="553" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>584</v>
       </c>
@@ -31612,7 +31637,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="554" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>584</v>
       </c>
@@ -31644,7 +31669,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="555" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>584</v>
       </c>
@@ -31676,7 +31701,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="556" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>584</v>
       </c>
@@ -31708,7 +31733,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="557" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>584</v>
       </c>
@@ -31740,7 +31765,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="558" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>584</v>
       </c>
@@ -31775,7 +31800,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="559" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>584</v>
       </c>
@@ -31810,7 +31835,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="560" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>584</v>
       </c>
@@ -31845,7 +31870,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="561" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>602</v>
       </c>
@@ -31880,7 +31905,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="562" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>602</v>
       </c>
@@ -31915,7 +31940,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="563" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>602</v>
       </c>
@@ -31950,7 +31975,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="564" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>602</v>
       </c>
@@ -31985,7 +32010,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="565" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>602</v>
       </c>
@@ -32020,7 +32045,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="566" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>602</v>
       </c>
@@ -32055,7 +32080,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="567" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>602</v>
       </c>
@@ -32090,7 +32115,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="568" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>602</v>
       </c>
@@ -32125,7 +32150,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="569" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>602</v>
       </c>
@@ -32160,7 +32185,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="570" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>602</v>
       </c>
@@ -35860,7 +35885,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="677" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>726</v>
       </c>
@@ -35907,7 +35932,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="678" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>726</v>
       </c>
@@ -35954,7 +35979,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="679" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>726</v>
       </c>
@@ -35995,7 +36020,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="680" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>726</v>
       </c>
@@ -36036,7 +36061,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="681" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>726</v>
       </c>
@@ -36080,7 +36105,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="682" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>726</v>
       </c>
@@ -36121,7 +36146,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="683" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>726</v>
       </c>
@@ -36162,7 +36187,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="684" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>726</v>
       </c>
@@ -36203,7 +36228,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="685" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>726</v>
       </c>
@@ -36244,7 +36269,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="686" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>726</v>
       </c>
@@ -36285,7 +36310,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="687" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>726</v>
       </c>
@@ -36326,7 +36351,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="688" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>726</v>
       </c>
@@ -36367,7 +36392,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="689" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>726</v>
       </c>
@@ -36408,7 +36433,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="690" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>726</v>
       </c>
@@ -36449,7 +36474,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="691" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>726</v>
       </c>
@@ -36490,7 +36515,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="692" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>726</v>
       </c>
@@ -36531,7 +36556,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="693" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>726</v>
       </c>
@@ -36572,7 +36597,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="694" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>726</v>
       </c>
@@ -36613,7 +36638,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="695" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>726</v>
       </c>
@@ -36654,7 +36679,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="696" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>726</v>
       </c>
@@ -36695,7 +36720,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="697" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>726</v>
       </c>
@@ -36736,7 +36761,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="698" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>726</v>
       </c>
@@ -36777,7 +36802,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="699" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>726</v>
       </c>
@@ -36818,7 +36843,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="700" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>726</v>
       </c>
@@ -36859,7 +36884,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="701" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>726</v>
       </c>
@@ -36894,7 +36919,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="702" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>726</v>
       </c>
@@ -36935,7 +36960,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="703" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>726</v>
       </c>
@@ -36976,7 +37001,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="704" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>726</v>
       </c>
@@ -37017,7 +37042,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="705" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>726</v>
       </c>
@@ -37058,7 +37083,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="706" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>726</v>
       </c>
@@ -37099,7 +37124,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="707" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>726</v>
       </c>
@@ -37140,7 +37165,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="708" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>726</v>
       </c>
@@ -37181,7 +37206,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="709" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>726</v>
       </c>
@@ -37222,7 +37247,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="710" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>726</v>
       </c>
@@ -37263,7 +37288,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="711" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>726</v>
       </c>
@@ -37298,7 +37323,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="712" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>726</v>
       </c>
@@ -37339,7 +37364,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="713" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>726</v>
       </c>
@@ -37380,7 +37405,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="714" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>726</v>
       </c>
@@ -37421,7 +37446,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="715" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>726</v>
       </c>
@@ -37462,7 +37487,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="716" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>726</v>
       </c>
@@ -37503,7 +37528,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="717" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>726</v>
       </c>
@@ -37535,7 +37560,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="718" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>726</v>
       </c>
@@ -37567,7 +37592,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="719" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>726</v>
       </c>
@@ -37605,7 +37630,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="720" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>726</v>
       </c>
@@ -37640,7 +37665,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="721" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>726</v>
       </c>
@@ -37675,7 +37700,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="722" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>726</v>
       </c>
@@ -37707,7 +37732,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="723" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>726</v>
       </c>
@@ -37739,7 +37764,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="724" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>726</v>
       </c>
@@ -38126,7 +38151,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="736" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>726</v>
       </c>
@@ -38167,7 +38192,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="737" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>726</v>
       </c>
@@ -38214,7 +38239,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="738" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>726</v>
       </c>
@@ -38255,7 +38280,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="739" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>726</v>
       </c>
@@ -38296,7 +38321,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="740" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>726</v>
       </c>
@@ -38337,7 +38362,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="741" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>726</v>
       </c>
@@ -38378,7 +38403,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="742" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>726</v>
       </c>
@@ -38419,7 +38444,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="743" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>726</v>
       </c>
@@ -38466,7 +38491,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="744" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>726</v>
       </c>
@@ -38507,7 +38532,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="745" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>726</v>
       </c>
@@ -38548,7 +38573,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="746" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>726</v>
       </c>
@@ -38589,7 +38614,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="747" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>726</v>
       </c>
@@ -38630,7 +38655,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="748" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>726</v>
       </c>
@@ -38671,7 +38696,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="749" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>726</v>
       </c>
@@ -38712,7 +38737,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="750" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>726</v>
       </c>
@@ -38753,7 +38778,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="751" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>726</v>
       </c>
@@ -38794,7 +38819,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="752" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>726</v>
       </c>
@@ -38835,7 +38860,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="753" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>726</v>
       </c>
@@ -38876,7 +38901,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="754" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>726</v>
       </c>
@@ -38917,7 +38942,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="755" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>726</v>
       </c>
@@ -38958,7 +38983,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="756" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>726</v>
       </c>
@@ -38999,7 +39024,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="757" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>726</v>
       </c>
@@ -39040,7 +39065,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="758" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>726</v>
       </c>
@@ -39081,7 +39106,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="759" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>726</v>
       </c>
@@ -39122,7 +39147,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="760" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>726</v>
       </c>
@@ -39163,7 +39188,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="761" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>726</v>
       </c>
@@ -39198,7 +39223,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="762" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>726</v>
       </c>
@@ -39236,7 +39261,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="763" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>726</v>
       </c>
@@ -39274,7 +39299,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="764" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>726</v>
       </c>
@@ -39312,7 +39337,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="765" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>726</v>
       </c>
@@ -39344,7 +39369,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="766" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>726</v>
       </c>
@@ -39382,7 +39407,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="767" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>726</v>
       </c>
@@ -40562,22 +40587,8 @@
         <v>446</v>
       </c>
     </row>
-    <row r="803" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A803" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B803" t="s">
-        <v>1047</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AP803" xr:uid="{93A70181-B22C-4671-9C22-4B8DA5FE66AB}">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="bugs"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AP803" xr:uid="{93A70181-B22C-4671-9C22-4B8DA5FE66AB}"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="C677:C724">
     <cfRule type="cellIs" dxfId="123" priority="16" operator="equal">
@@ -40585,69 +40596,69 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D560">
-    <cfRule type="cellIs" dxfId="122" priority="124" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="123" operator="equal">
+      <formula>"NA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="121" priority="124" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="123" operator="equal">
-      <formula>"NA"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="120" priority="125" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D562:D563 D568:D569 D571:D575 D577 D579:D581 D583 D586 D588:D590 D607:D608 D613 D627:D628 D655:D656 D659 D663:D665 D667">
-    <cfRule type="cellIs" dxfId="119" priority="99" operator="equal">
-      <formula>"Increase"</formula>
+    <cfRule type="cellIs" dxfId="119" priority="97" operator="equal">
+      <formula>"NA"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="118" priority="98" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="97" operator="equal">
-      <formula>"NA"</formula>
+    <cfRule type="cellIs" dxfId="117" priority="99" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D596:D598 D604">
-    <cfRule type="cellIs" dxfId="116" priority="87" operator="equal">
-      <formula>"Increase"</formula>
+    <cfRule type="cellIs" dxfId="116" priority="85" operator="equal">
+      <formula>"NA"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="115" priority="86" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="85" operator="equal">
-      <formula>"NA"</formula>
+    <cfRule type="cellIs" dxfId="114" priority="87" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D617:D618 D623">
-    <cfRule type="cellIs" dxfId="113" priority="83" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="82" operator="equal">
+      <formula>"NA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="112" priority="83" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="82" operator="equal">
-      <formula>"NA"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="111" priority="84" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D637:D638">
-    <cfRule type="cellIs" dxfId="110" priority="81" operator="equal">
-      <formula>"Increase"</formula>
+    <cfRule type="cellIs" dxfId="110" priority="79" operator="equal">
+      <formula>"NA"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="109" priority="80" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="79" operator="equal">
-      <formula>"NA"</formula>
+    <cfRule type="cellIs" dxfId="108" priority="81" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D647:D648">
-    <cfRule type="cellIs" dxfId="107" priority="78" operator="equal">
-      <formula>"Increase"</formula>
+    <cfRule type="cellIs" dxfId="107" priority="76" operator="equal">
+      <formula>"NA"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="106" priority="77" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="76" operator="equal">
-      <formula>"NA"</formula>
+    <cfRule type="cellIs" dxfId="105" priority="78" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D670:D682">
@@ -40662,36 +40673,36 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D684">
-    <cfRule type="cellIs" dxfId="101" priority="33" operator="equal">
-      <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="31" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="32" operator="equal">
       <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="99" priority="33" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D686">
-    <cfRule type="cellIs" dxfId="98" priority="36" operator="equal">
-      <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="34" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="35" operator="equal">
       <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="96" priority="36" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D691:D694">
-    <cfRule type="cellIs" dxfId="95" priority="39" operator="equal">
-      <formula>"Increase"</formula>
+    <cfRule type="cellIs" dxfId="95" priority="37" operator="equal">
+      <formula>"NA"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="94" priority="38" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="37" operator="equal">
-      <formula>"NA"</formula>
+    <cfRule type="cellIs" dxfId="93" priority="39" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D697">
@@ -40706,14 +40717,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D706:D707">
-    <cfRule type="cellIs" dxfId="89" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="22" operator="equal">
+      <formula>"NA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="88" priority="23" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="24" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="22" operator="equal">
-      <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D714:D716">
@@ -40731,11 +40742,11 @@
     <cfRule type="cellIs" dxfId="83" priority="46" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="47" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="81" priority="48" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="47" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D726:D727">
@@ -40750,36 +40761,36 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D730:D731">
-    <cfRule type="cellIs" dxfId="77" priority="58" operator="equal">
-      <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="56" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="56" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="57" operator="equal">
       <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="75" priority="58" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D733">
-    <cfRule type="cellIs" dxfId="74" priority="54" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="53" operator="equal">
+      <formula>"NA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="54" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="53" operator="equal">
-      <formula>"NA"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="72" priority="55" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D735:D802">
-    <cfRule type="cellIs" dxfId="71" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="1" operator="equal">
+      <formula>"NA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="70" priority="2" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="3" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="1" operator="equal">
-      <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E197:E202 E214 E226:F226 E238:F238 E250:F250">
@@ -40799,19 +40810,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E401 E413 E425 E437:F437 E449:F449">
-    <cfRule type="cellIs" dxfId="64" priority="275" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="274" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="275" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="274" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E407:E410">
-    <cfRule type="cellIs" dxfId="62" priority="207" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="206" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="207" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="206" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E415 E418">
@@ -40823,27 +40834,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E427">
-    <cfRule type="cellIs" dxfId="58" priority="229" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="228" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="57" priority="229" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="228" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E430">
-    <cfRule type="cellIs" dxfId="56" priority="184" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="183" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="55" priority="184" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="183" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E262:F263 F264">
-    <cfRule type="cellIs" dxfId="54" priority="427" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="426" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="53" priority="427" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="426" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E269:F269 F270">
@@ -40855,19 +40866,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E403:F403">
-    <cfRule type="cellIs" dxfId="50" priority="195" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="194" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="195" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="194" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E461:F463">
-    <cfRule type="cellIs" dxfId="48" priority="227" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="226" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="47" priority="227" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="226" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E468:F469">
@@ -40879,19 +40890,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F191 E192:F192">
-    <cfRule type="cellIs" dxfId="44" priority="522" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="521" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="522" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="521" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F193:F214">
-    <cfRule type="cellIs" dxfId="42" priority="452" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="451" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="41" priority="452" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="451" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F236">
@@ -40903,27 +40914,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F260">
-    <cfRule type="cellIs" dxfId="38" priority="458" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="457" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="458" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="457" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F390 E391:F391 E396:E399">
-    <cfRule type="cellIs" dxfId="36" priority="334" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="333" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="35" priority="334" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="333" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F392:F402">
-    <cfRule type="cellIs" dxfId="34" priority="201" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="200" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="201" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="200" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F404:F414">
@@ -40951,11 +40962,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F459">
-    <cfRule type="cellIs" dxfId="26" priority="291" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="290" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="291" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="290" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H191:H274">
@@ -40996,11 +41007,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O411 O435 O459">
-    <cfRule type="cellIs" dxfId="15" priority="281" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="280" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="281" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="280" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O174:P192 O390:P391">
@@ -41079,7 +41090,7 @@
   <sheetPr filterMode="1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:Z122"/>
+  <dimension ref="A1:Z110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
@@ -47952,677 +47963,8 @@
         <v>446</v>
       </c>
     </row>
-    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B111" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C111" t="s">
-        <v>100</v>
-      </c>
-      <c r="D111">
-        <v>4</v>
-      </c>
-      <c r="E111" t="s">
-        <v>106</v>
-      </c>
-      <c r="G111" t="s">
-        <v>99</v>
-      </c>
-      <c r="H111">
-        <v>4</v>
-      </c>
-      <c r="I111">
-        <v>1</v>
-      </c>
-      <c r="J111">
-        <v>2</v>
-      </c>
-      <c r="K111">
-        <v>2.65</v>
-      </c>
-      <c r="L111">
-        <v>3</v>
-      </c>
-      <c r="M111">
-        <v>5</v>
-      </c>
-      <c r="P111" t="s">
-        <v>415</v>
-      </c>
-      <c r="Q111" t="s">
-        <v>407</v>
-      </c>
-      <c r="R111" t="s">
-        <v>1050</v>
-      </c>
-      <c r="S111" t="s">
-        <v>1049</v>
-      </c>
-      <c r="V111" t="b">
-        <v>0</v>
-      </c>
-      <c r="W111" t="s">
-        <v>78</v>
-      </c>
-      <c r="X111" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y111" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B112" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C112" t="s">
-        <v>100</v>
-      </c>
-      <c r="D112">
-        <v>6</v>
-      </c>
-      <c r="E112" t="s">
-        <v>106</v>
-      </c>
-      <c r="G112" t="s">
-        <v>99</v>
-      </c>
-      <c r="H112">
-        <v>4</v>
-      </c>
-      <c r="I112">
-        <v>1</v>
-      </c>
-      <c r="J112">
-        <v>2</v>
-      </c>
-      <c r="K112">
-        <v>2.65</v>
-      </c>
-      <c r="L112">
-        <v>3</v>
-      </c>
-      <c r="M112">
-        <v>5</v>
-      </c>
-      <c r="P112" t="s">
-        <v>415</v>
-      </c>
-      <c r="Q112" t="s">
-        <v>407</v>
-      </c>
-      <c r="R112" t="s">
-        <v>1050</v>
-      </c>
-      <c r="S112" t="s">
-        <v>1049</v>
-      </c>
-      <c r="V112" t="b">
-        <v>0</v>
-      </c>
-      <c r="W112" t="s">
-        <v>78</v>
-      </c>
-      <c r="X112" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y112" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B113" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C113" t="s">
-        <v>100</v>
-      </c>
-      <c r="D113">
-        <v>6</v>
-      </c>
-      <c r="E113" t="s">
-        <v>106</v>
-      </c>
-      <c r="G113" t="s">
-        <v>99</v>
-      </c>
-      <c r="H113">
-        <v>4</v>
-      </c>
-      <c r="I113">
-        <v>1</v>
-      </c>
-      <c r="J113">
-        <v>2</v>
-      </c>
-      <c r="K113">
-        <v>2.65</v>
-      </c>
-      <c r="L113">
-        <v>3</v>
-      </c>
-      <c r="M113">
-        <v>5</v>
-      </c>
-      <c r="P113" t="s">
-        <v>415</v>
-      </c>
-      <c r="Q113" t="s">
-        <v>407</v>
-      </c>
-      <c r="R113" t="s">
-        <v>1050</v>
-      </c>
-      <c r="S113" t="s">
-        <v>1049</v>
-      </c>
-      <c r="V113" t="b">
-        <v>0</v>
-      </c>
-      <c r="W113" t="s">
-        <v>78</v>
-      </c>
-      <c r="X113" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y113" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B114" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C114" t="s">
-        <v>100</v>
-      </c>
-      <c r="D114">
-        <v>6</v>
-      </c>
-      <c r="E114" t="s">
-        <v>106</v>
-      </c>
-      <c r="G114" t="s">
-        <v>99</v>
-      </c>
-      <c r="H114">
-        <v>4</v>
-      </c>
-      <c r="I114">
-        <v>1</v>
-      </c>
-      <c r="J114">
-        <v>2</v>
-      </c>
-      <c r="K114">
-        <v>2.65</v>
-      </c>
-      <c r="L114">
-        <v>3</v>
-      </c>
-      <c r="M114">
-        <v>5</v>
-      </c>
-      <c r="P114" t="s">
-        <v>415</v>
-      </c>
-      <c r="Q114" t="s">
-        <v>407</v>
-      </c>
-      <c r="R114" t="s">
-        <v>1050</v>
-      </c>
-      <c r="S114" t="s">
-        <v>1049</v>
-      </c>
-      <c r="V114" t="b">
-        <v>0</v>
-      </c>
-      <c r="W114" t="s">
-        <v>78</v>
-      </c>
-      <c r="X114" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y114" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B115" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C115" t="s">
-        <v>100</v>
-      </c>
-      <c r="D115">
-        <v>7</v>
-      </c>
-      <c r="E115" t="s">
-        <v>106</v>
-      </c>
-      <c r="G115" t="s">
-        <v>99</v>
-      </c>
-      <c r="H115">
-        <v>4</v>
-      </c>
-      <c r="I115">
-        <v>1</v>
-      </c>
-      <c r="J115">
-        <v>2</v>
-      </c>
-      <c r="K115">
-        <v>2.65</v>
-      </c>
-      <c r="L115">
-        <v>3</v>
-      </c>
-      <c r="M115">
-        <v>5</v>
-      </c>
-      <c r="P115" t="s">
-        <v>415</v>
-      </c>
-      <c r="Q115" t="s">
-        <v>407</v>
-      </c>
-      <c r="R115" t="s">
-        <v>1050</v>
-      </c>
-      <c r="S115" t="s">
-        <v>1049</v>
-      </c>
-      <c r="V115" t="b">
-        <v>0</v>
-      </c>
-      <c r="W115" t="s">
-        <v>78</v>
-      </c>
-      <c r="X115" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y115" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B116" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C116" t="s">
-        <v>100</v>
-      </c>
-      <c r="D116">
-        <v>6</v>
-      </c>
-      <c r="E116" t="s">
-        <v>106</v>
-      </c>
-      <c r="G116" t="s">
-        <v>99</v>
-      </c>
-      <c r="H116">
-        <v>4</v>
-      </c>
-      <c r="I116">
-        <v>1</v>
-      </c>
-      <c r="J116">
-        <v>2</v>
-      </c>
-      <c r="K116">
-        <v>2.65</v>
-      </c>
-      <c r="L116">
-        <v>3</v>
-      </c>
-      <c r="M116">
-        <v>5</v>
-      </c>
-      <c r="P116" t="s">
-        <v>415</v>
-      </c>
-      <c r="Q116" t="s">
-        <v>407</v>
-      </c>
-      <c r="R116" t="s">
-        <v>1050</v>
-      </c>
-      <c r="S116" t="s">
-        <v>1049</v>
-      </c>
-      <c r="V116" t="b">
-        <v>0</v>
-      </c>
-      <c r="W116" t="s">
-        <v>78</v>
-      </c>
-      <c r="X116" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y116" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B117" t="s">
-        <v>1055</v>
-      </c>
-      <c r="C117" t="s">
-        <v>100</v>
-      </c>
-      <c r="D117">
-        <v>7</v>
-      </c>
-      <c r="E117" t="s">
-        <v>106</v>
-      </c>
-      <c r="G117" t="s">
-        <v>99</v>
-      </c>
-      <c r="H117">
-        <v>4</v>
-      </c>
-      <c r="I117">
-        <v>1</v>
-      </c>
-      <c r="J117">
-        <v>2</v>
-      </c>
-      <c r="K117">
-        <v>2.65</v>
-      </c>
-      <c r="L117">
-        <v>3</v>
-      </c>
-      <c r="M117">
-        <v>5</v>
-      </c>
-      <c r="P117" t="s">
-        <v>415</v>
-      </c>
-      <c r="Q117" t="s">
-        <v>407</v>
-      </c>
-      <c r="R117" t="s">
-        <v>1050</v>
-      </c>
-      <c r="S117" t="s">
-        <v>1049</v>
-      </c>
-      <c r="V117" t="b">
-        <v>0</v>
-      </c>
-      <c r="W117" t="s">
-        <v>78</v>
-      </c>
-      <c r="X117" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y117" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B118" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C118" t="s">
-        <v>100</v>
-      </c>
-      <c r="E118" t="s">
-        <v>106</v>
-      </c>
-      <c r="G118" t="s">
-        <v>99</v>
-      </c>
-      <c r="H118">
-        <v>4</v>
-      </c>
-      <c r="I118">
-        <v>1</v>
-      </c>
-      <c r="J118">
-        <v>2</v>
-      </c>
-      <c r="K118">
-        <v>2.65</v>
-      </c>
-      <c r="L118">
-        <v>3</v>
-      </c>
-      <c r="M118">
-        <v>5</v>
-      </c>
-      <c r="P118" t="s">
-        <v>415</v>
-      </c>
-      <c r="Q118" t="s">
-        <v>407</v>
-      </c>
-      <c r="R118" t="s">
-        <v>1050</v>
-      </c>
-      <c r="S118" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B119" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C119" t="s">
-        <v>100</v>
-      </c>
-      <c r="E119" t="s">
-        <v>106</v>
-      </c>
-      <c r="G119" t="s">
-        <v>99</v>
-      </c>
-      <c r="H119">
-        <v>4</v>
-      </c>
-      <c r="I119">
-        <v>1</v>
-      </c>
-      <c r="J119">
-        <v>2</v>
-      </c>
-      <c r="K119">
-        <v>2.65</v>
-      </c>
-      <c r="L119">
-        <v>3</v>
-      </c>
-      <c r="M119">
-        <v>5</v>
-      </c>
-      <c r="P119" t="s">
-        <v>415</v>
-      </c>
-      <c r="Q119" t="s">
-        <v>407</v>
-      </c>
-      <c r="R119" t="s">
-        <v>1050</v>
-      </c>
-      <c r="S119" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B120" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C120" t="s">
-        <v>100</v>
-      </c>
-      <c r="E120" t="s">
-        <v>106</v>
-      </c>
-      <c r="G120" t="s">
-        <v>99</v>
-      </c>
-      <c r="H120">
-        <v>4</v>
-      </c>
-      <c r="I120">
-        <v>1</v>
-      </c>
-      <c r="J120">
-        <v>2</v>
-      </c>
-      <c r="K120">
-        <v>2.65</v>
-      </c>
-      <c r="L120">
-        <v>3</v>
-      </c>
-      <c r="M120">
-        <v>5</v>
-      </c>
-      <c r="P120" t="s">
-        <v>415</v>
-      </c>
-      <c r="Q120" t="s">
-        <v>407</v>
-      </c>
-      <c r="R120" t="s">
-        <v>1050</v>
-      </c>
-      <c r="S120" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B121" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C121" t="s">
-        <v>100</v>
-      </c>
-      <c r="E121" t="s">
-        <v>106</v>
-      </c>
-      <c r="G121" t="s">
-        <v>99</v>
-      </c>
-      <c r="H121">
-        <v>4</v>
-      </c>
-      <c r="I121">
-        <v>1</v>
-      </c>
-      <c r="J121">
-        <v>2</v>
-      </c>
-      <c r="K121">
-        <v>2.65</v>
-      </c>
-      <c r="L121">
-        <v>3</v>
-      </c>
-      <c r="M121">
-        <v>5</v>
-      </c>
-      <c r="P121" t="s">
-        <v>415</v>
-      </c>
-      <c r="Q121" t="s">
-        <v>407</v>
-      </c>
-      <c r="R121" t="s">
-        <v>1050</v>
-      </c>
-      <c r="S121" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B122" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C122" t="s">
-        <v>100</v>
-      </c>
-      <c r="E122" t="s">
-        <v>106</v>
-      </c>
-      <c r="G122" t="s">
-        <v>99</v>
-      </c>
-      <c r="H122">
-        <v>4</v>
-      </c>
-      <c r="I122">
-        <v>1</v>
-      </c>
-      <c r="J122">
-        <v>2</v>
-      </c>
-      <c r="K122">
-        <v>2.65</v>
-      </c>
-      <c r="L122">
-        <v>3</v>
-      </c>
-      <c r="M122">
-        <v>5</v>
-      </c>
-      <c r="P122" t="s">
-        <v>415</v>
-      </c>
-      <c r="Q122" t="s">
-        <v>407</v>
-      </c>
-      <c r="R122" t="s">
-        <v>1050</v>
-      </c>
-      <c r="S122" t="s">
-        <v>1049</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Z117" xr:uid="{544F088F-E018-4AF1-A817-C6B9859D0A47}">
+  <autoFilter ref="A1:Z110" xr:uid="{544F088F-E018-4AF1-A817-C6B9859D0A47}">
     <filterColumn colId="0">
       <filters>
         <filter val="ChesBay_2002"/>
@@ -48639,7 +47981,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BB61F63-921C-4D79-B43A-73F58D6664BB}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
@@ -48679,7 +48021,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="str" cm="1">
-        <f t="array" ref="A4:A30">_xlfn.UNIQUE(metric.scoring!A2:A988)</f>
+        <f t="array" ref="A4:A29">_xlfn.UNIQUE(metric.scoring!A2:A988)</f>
         <v>MBSS_2005_Bugs</v>
       </c>
       <c r="B4" cm="1">
@@ -49104,12 +48446,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="str">
-        <v>ChesBay_2002</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30">
+      <c r="A29">
         <v>0</v>
       </c>
     </row>
@@ -51032,8 +50369,8 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B040EC47-1904-4F3A-82A5-2E328A8FF41E}">
-  <dimension ref="A1:Z11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B040EC47-1904-4F3A-82A5-2E328A8FF41E}">
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -51472,9 +50809,767 @@
         <v>446</v>
       </c>
     </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="33">
+        <v>46160</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>667</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>579</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="M16" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="O16" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="P16" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q16" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="R16" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="S16" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="T16" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="U16" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="V16" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="W16" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="X16" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y16" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="Z16" s="13" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17">
+        <v>4</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17">
+        <v>2.65</v>
+      </c>
+      <c r="L17">
+        <v>3</v>
+      </c>
+      <c r="M17">
+        <v>5</v>
+      </c>
+      <c r="P17" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>407</v>
+      </c>
+      <c r="R17" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S17" t="s">
+        <v>1049</v>
+      </c>
+      <c r="V17" t="b">
+        <v>0</v>
+      </c>
+      <c r="W17" t="s">
+        <v>78</v>
+      </c>
+      <c r="X17" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+      <c r="E18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18">
+        <v>4</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18">
+        <v>2.65</v>
+      </c>
+      <c r="L18">
+        <v>3</v>
+      </c>
+      <c r="M18">
+        <v>5</v>
+      </c>
+      <c r="P18" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>407</v>
+      </c>
+      <c r="R18" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S18" t="s">
+        <v>1049</v>
+      </c>
+      <c r="V18" t="b">
+        <v>0</v>
+      </c>
+      <c r="W18" t="s">
+        <v>78</v>
+      </c>
+      <c r="X18" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19">
+        <v>6</v>
+      </c>
+      <c r="E19" t="s">
+        <v>106</v>
+      </c>
+      <c r="G19" t="s">
+        <v>99</v>
+      </c>
+      <c r="H19">
+        <v>4</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <v>2.65</v>
+      </c>
+      <c r="L19">
+        <v>3</v>
+      </c>
+      <c r="M19">
+        <v>5</v>
+      </c>
+      <c r="P19" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>407</v>
+      </c>
+      <c r="R19" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S19" t="s">
+        <v>1049</v>
+      </c>
+      <c r="V19" t="b">
+        <v>0</v>
+      </c>
+      <c r="W19" t="s">
+        <v>78</v>
+      </c>
+      <c r="X19" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20">
+        <v>6</v>
+      </c>
+      <c r="E20" t="s">
+        <v>106</v>
+      </c>
+      <c r="G20" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20">
+        <v>4</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>2</v>
+      </c>
+      <c r="K20">
+        <v>2.65</v>
+      </c>
+      <c r="L20">
+        <v>3</v>
+      </c>
+      <c r="M20">
+        <v>5</v>
+      </c>
+      <c r="P20" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>407</v>
+      </c>
+      <c r="R20" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S20" t="s">
+        <v>1049</v>
+      </c>
+      <c r="V20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W20" t="s">
+        <v>78</v>
+      </c>
+      <c r="X20" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21">
+        <v>7</v>
+      </c>
+      <c r="E21" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H21">
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21">
+        <v>2.65</v>
+      </c>
+      <c r="L21">
+        <v>3</v>
+      </c>
+      <c r="M21">
+        <v>5</v>
+      </c>
+      <c r="P21" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>407</v>
+      </c>
+      <c r="R21" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S21" t="s">
+        <v>1049</v>
+      </c>
+      <c r="V21" t="b">
+        <v>0</v>
+      </c>
+      <c r="W21" t="s">
+        <v>78</v>
+      </c>
+      <c r="X21" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C22" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22">
+        <v>6</v>
+      </c>
+      <c r="E22" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" t="s">
+        <v>99</v>
+      </c>
+      <c r="H22">
+        <v>4</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <v>2.65</v>
+      </c>
+      <c r="L22">
+        <v>3</v>
+      </c>
+      <c r="M22">
+        <v>5</v>
+      </c>
+      <c r="P22" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>407</v>
+      </c>
+      <c r="R22" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S22" t="s">
+        <v>1049</v>
+      </c>
+      <c r="V22" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" t="s">
+        <v>78</v>
+      </c>
+      <c r="X22" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23">
+        <v>7</v>
+      </c>
+      <c r="E23" t="s">
+        <v>106</v>
+      </c>
+      <c r="G23" t="s">
+        <v>99</v>
+      </c>
+      <c r="H23">
+        <v>4</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>2</v>
+      </c>
+      <c r="K23">
+        <v>2.65</v>
+      </c>
+      <c r="L23">
+        <v>3</v>
+      </c>
+      <c r="M23">
+        <v>5</v>
+      </c>
+      <c r="P23" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>407</v>
+      </c>
+      <c r="R23" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S23" t="s">
+        <v>1049</v>
+      </c>
+      <c r="V23" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" t="s">
+        <v>78</v>
+      </c>
+      <c r="X23" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C24" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" t="s">
+        <v>99</v>
+      </c>
+      <c r="H24">
+        <v>4</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>2</v>
+      </c>
+      <c r="K24">
+        <v>2.65</v>
+      </c>
+      <c r="L24">
+        <v>3</v>
+      </c>
+      <c r="M24">
+        <v>5</v>
+      </c>
+      <c r="P24" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>407</v>
+      </c>
+      <c r="R24" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S24" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C25" t="s">
+        <v>100</v>
+      </c>
+      <c r="E25" t="s">
+        <v>106</v>
+      </c>
+      <c r="G25" t="s">
+        <v>99</v>
+      </c>
+      <c r="H25">
+        <v>4</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25">
+        <v>2.65</v>
+      </c>
+      <c r="L25">
+        <v>3</v>
+      </c>
+      <c r="M25">
+        <v>5</v>
+      </c>
+      <c r="P25" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>407</v>
+      </c>
+      <c r="R25" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S25" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C26" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" t="s">
+        <v>99</v>
+      </c>
+      <c r="H26">
+        <v>4</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26">
+        <v>2.65</v>
+      </c>
+      <c r="L26">
+        <v>3</v>
+      </c>
+      <c r="M26">
+        <v>5</v>
+      </c>
+      <c r="P26" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>407</v>
+      </c>
+      <c r="R26" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S26" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" t="s">
+        <v>99</v>
+      </c>
+      <c r="H27">
+        <v>4</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="K27">
+        <v>2.65</v>
+      </c>
+      <c r="L27">
+        <v>3</v>
+      </c>
+      <c r="M27">
+        <v>5</v>
+      </c>
+      <c r="P27" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>407</v>
+      </c>
+      <c r="R27" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S27" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C28" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" t="s">
+        <v>106</v>
+      </c>
+      <c r="G28" t="s">
+        <v>99</v>
+      </c>
+      <c r="H28">
+        <v>4</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>2</v>
+      </c>
+      <c r="K28">
+        <v>2.65</v>
+      </c>
+      <c r="L28">
+        <v>3</v>
+      </c>
+      <c r="M28">
+        <v>5</v>
+      </c>
+      <c r="P28" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>407</v>
+      </c>
+      <c r="R28" t="s">
+        <v>1050</v>
+      </c>
+      <c r="S28" t="s">
+        <v>1049</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
